--- a/database/15-RES_hh_tes.xlsx
+++ b/database/15-RES_hh_tes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\109192\OneDrive - Fundacion Tecnalia Research &amp; Innovation\ESCRITORIO\Ciudades\iDesignRES\Enerkad\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\git\buildings\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4489598F-76F7-42DF-999A-4E2430255BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F307CB3-BEE7-4E23-8878-A789A31470E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D3CA8CBF-D0C1-4D06-993D-3A172832AF0F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3CA8CBF-D0C1-4D06-993D-3A172832AF0F}"/>
   </bookViews>
   <sheets>
     <sheet name="RES_hh_tes (%)" sheetId="1" r:id="rId1"/>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>Energy service</t>
   </si>
@@ -303,9 +303,6 @@
     <t>Hydrogen</t>
   </si>
   <si>
-    <t>_Electricity in circulation</t>
-  </si>
-  <si>
     <t>Electricity in circulation</t>
   </si>
   <si>
@@ -451,6 +448,12 @@
   </si>
   <si>
     <t>Water heating_Advanced electric heating</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Space heating_Electricity in circulation</t>
   </si>
 </sst>
 </file>
@@ -622,7 +625,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -655,6 +658,7 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares 3" xfId="3" xr:uid="{9D330414-D2A3-4933-A75C-3C8A364275F6}"/>
@@ -1120,23 +1124,23 @@
   <sheetPr codeName="Hoja68">
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -1148,7 +1152,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
@@ -1187,13 +1191,13 @@
         <v>15</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>17</v>
@@ -1205,10 +1209,10 @@
         <v>19</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>20</v>
@@ -1217,7 +1221,7 @@
         <v>21</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>22</v>
@@ -1229,7 +1233,7 @@
         <v>24</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AI1" s="2" t="s">
         <v>25</v>
@@ -1241,21 +1245,24 @@
         <v>27</v>
       </c>
       <c r="AL1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="AN1" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AO1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
@@ -1377,8 +1384,11 @@
       <c r="AO2" s="4">
         <v>1</v>
       </c>
+      <c r="AP2" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
@@ -1502,8 +1512,11 @@
       <c r="AO3" s="7">
         <v>3.0240676427477773E-2</v>
       </c>
+      <c r="AP3" s="7">
+        <v>3.0240676427477773E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -1627,8 +1640,11 @@
       <c r="AO4" s="7">
         <v>1.2518193117781035E-2</v>
       </c>
+      <c r="AP4" s="7">
+        <v>1.2518193117781035E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>34</v>
       </c>
@@ -1752,8 +1768,11 @@
       <c r="AO5" s="7">
         <v>8.0664870072846784E-2</v>
       </c>
+      <c r="AP5" s="7">
+        <v>8.0664870072846784E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>36</v>
       </c>
@@ -1877,8 +1896,11 @@
       <c r="AO6" s="7">
         <v>0</v>
       </c>
+      <c r="AP6" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>38</v>
       </c>
@@ -2002,8 +2024,11 @@
       <c r="AO7" s="7">
         <v>0.38580352338530277</v>
       </c>
+      <c r="AP7" s="7">
+        <v>0.38580352338530277</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>40</v>
       </c>
@@ -2127,8 +2152,11 @@
       <c r="AO8" s="7">
         <v>0.21710117759245112</v>
       </c>
+      <c r="AP8" s="7">
+        <v>0.21710117759245112</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
@@ -2252,8 +2280,11 @@
       <c r="AO9" s="7">
         <v>3.5469885065176189E-4</v>
       </c>
+      <c r="AP9" s="7">
+        <v>3.5469885065176189E-4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
@@ -2377,8 +2408,11 @@
       <c r="AO10" s="7">
         <v>0.11754795563781997</v>
       </c>
+      <c r="AP10" s="7">
+        <v>0.11754795563781997</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
@@ -2502,8 +2536,11 @@
       <c r="AO11" s="7">
         <v>9.9107251170834951E-2</v>
       </c>
+      <c r="AP11" s="7">
+        <v>9.9107251170834951E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>48</v>
       </c>
@@ -2627,8 +2664,11 @@
       <c r="AO12" s="7">
         <v>4.578659523529565E-2</v>
       </c>
+      <c r="AP12" s="7">
+        <v>4.578659523529565E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -2752,8 +2792,11 @@
       <c r="AO13" s="7">
         <v>0</v>
       </c>
+      <c r="AP13" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>52</v>
       </c>
@@ -2877,8 +2920,11 @@
       <c r="AO14" s="7">
         <v>0</v>
       </c>
+      <c r="AP14" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>54</v>
       </c>
@@ -3002,13 +3048,16 @@
       <c r="AO15" s="7">
         <v>0</v>
       </c>
+      <c r="AP15" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="C16" s="7">
         <v>1.0875058509537966E-2</v>
@@ -3127,13 +3176,16 @@
       <c r="AO16" s="7">
         <v>1.0875058509537966E-2</v>
       </c>
+      <c r="AP16" s="7">
+        <v>1.0875058509537966E-2</v>
+      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C17" s="4">
         <v>0.19575193429842577</v>
@@ -3252,10 +3304,13 @@
       <c r="AO17" s="4">
         <v>0.19575193429842577</v>
       </c>
+      <c r="AP17" s="4">
+        <v>0.19575193429842577</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>37</v>
@@ -3377,260 +3432,269 @@
       <c r="AO18" s="9">
         <v>0</v>
       </c>
+      <c r="AP18" s="9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1</v>
+      </c>
+      <c r="K19" s="7">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="7">
+        <v>1</v>
+      </c>
+      <c r="O19" s="7">
+        <v>1</v>
+      </c>
+      <c r="P19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>1</v>
+      </c>
+      <c r="R19" s="7">
+        <v>1</v>
+      </c>
+      <c r="S19" s="7">
+        <v>1</v>
+      </c>
+      <c r="T19" s="7">
+        <v>1</v>
+      </c>
+      <c r="U19" s="7">
+        <v>1</v>
+      </c>
+      <c r="V19" s="7">
+        <v>1</v>
+      </c>
+      <c r="W19" s="7">
+        <v>1</v>
+      </c>
+      <c r="X19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP19" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="7">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7">
-        <v>1</v>
-      </c>
-      <c r="I19" s="7">
-        <v>1</v>
-      </c>
-      <c r="J19" s="7">
-        <v>1</v>
-      </c>
-      <c r="K19" s="7">
-        <v>1</v>
-      </c>
-      <c r="L19" s="7">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7">
-        <v>1</v>
-      </c>
-      <c r="N19" s="7">
-        <v>1</v>
-      </c>
-      <c r="O19" s="7">
-        <v>1</v>
-      </c>
-      <c r="P19" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="7">
-        <v>1</v>
-      </c>
-      <c r="R19" s="7">
-        <v>1</v>
-      </c>
-      <c r="S19" s="7">
-        <v>1</v>
-      </c>
-      <c r="T19" s="7">
-        <v>1</v>
-      </c>
-      <c r="U19" s="7">
-        <v>1</v>
-      </c>
-      <c r="V19" s="7">
-        <v>1</v>
-      </c>
-      <c r="W19" s="7">
-        <v>1</v>
-      </c>
-      <c r="X19" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN19" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO19" s="7">
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1</v>
+      </c>
+      <c r="L20" s="4">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4">
+        <v>1</v>
+      </c>
+      <c r="N20" s="4">
+        <v>1</v>
+      </c>
+      <c r="O20" s="4">
+        <v>1</v>
+      </c>
+      <c r="P20" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>1</v>
+      </c>
+      <c r="R20" s="4">
+        <v>1</v>
+      </c>
+      <c r="S20" s="4">
+        <v>1</v>
+      </c>
+      <c r="T20" s="4">
+        <v>1</v>
+      </c>
+      <c r="U20" s="4">
+        <v>1</v>
+      </c>
+      <c r="V20" s="4">
+        <v>1</v>
+      </c>
+      <c r="W20" s="4">
+        <v>1</v>
+      </c>
+      <c r="X20" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>64</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4">
-        <v>1</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4">
-        <v>1</v>
-      </c>
-      <c r="K20" s="4">
-        <v>1</v>
-      </c>
-      <c r="L20" s="4">
-        <v>1</v>
-      </c>
-      <c r="M20" s="4">
-        <v>1</v>
-      </c>
-      <c r="N20" s="4">
-        <v>1</v>
-      </c>
-      <c r="O20" s="4">
-        <v>1</v>
-      </c>
-      <c r="P20" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>1</v>
-      </c>
-      <c r="R20" s="4">
-        <v>1</v>
-      </c>
-      <c r="S20" s="4">
-        <v>1</v>
-      </c>
-      <c r="T20" s="4">
-        <v>1</v>
-      </c>
-      <c r="U20" s="4">
-        <v>1</v>
-      </c>
-      <c r="V20" s="4">
-        <v>1</v>
-      </c>
-      <c r="W20" s="4">
-        <v>1</v>
-      </c>
-      <c r="X20" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AL20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AN20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AO20" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>65</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>31</v>
@@ -3752,10 +3816,13 @@
       <c r="AO21" s="7">
         <v>1.6158596644350313E-2</v>
       </c>
+      <c r="AP21" s="7">
+        <v>1.6158596644350313E-2</v>
+      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>33</v>
@@ -3877,10 +3944,13 @@
       <c r="AO22" s="7">
         <v>3.7376338764954511E-2</v>
       </c>
+      <c r="AP22" s="7">
+        <v>3.7376338764954511E-2</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>35</v>
@@ -4002,10 +4072,13 @@
       <c r="AO23" s="7">
         <v>7.0503295552177631E-2</v>
       </c>
+      <c r="AP23" s="7">
+        <v>7.0503295552177631E-2</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>39</v>
@@ -4127,10 +4200,13 @@
       <c r="AO24" s="7">
         <v>0.37586071948258948</v>
       </c>
+      <c r="AP24" s="7">
+        <v>0.37586071948258948</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>41</v>
@@ -4252,10 +4328,13 @@
       <c r="AO25" s="7">
         <v>9.1410335212849164E-2</v>
       </c>
+      <c r="AP25" s="7">
+        <v>9.1410335212849164E-2</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>43</v>
@@ -4377,10 +4456,13 @@
       <c r="AO26" s="7">
         <v>2.1461188548714132E-4</v>
       </c>
+      <c r="AP26" s="7">
+        <v>2.1461188548714132E-4</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>45</v>
@@ -4502,10 +4584,13 @@
       <c r="AO27" s="7">
         <v>8.4609977348954285E-2</v>
       </c>
+      <c r="AP27" s="7">
+        <v>8.4609977348954285E-2</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>105</v>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>47</v>
@@ -4627,13 +4712,16 @@
       <c r="AO28" s="7">
         <v>0</v>
       </c>
+      <c r="AP28" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="C29" s="7">
         <v>0.23031949530862714</v>
@@ -4752,10 +4840,13 @@
       <c r="AO29" s="7">
         <v>0.23031949530862714</v>
       </c>
+      <c r="AP29" s="7">
+        <v>0.23031949530862714</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>51</v>
@@ -4877,10 +4968,13 @@
       <c r="AO30" s="7">
         <v>0</v>
       </c>
+      <c r="AP30" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>53</v>
@@ -5002,10 +5096,13 @@
       <c r="AO31" s="7">
         <v>0</v>
       </c>
+      <c r="AP31" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>55</v>
@@ -5127,13 +5224,16 @@
       <c r="AO32" s="7">
         <v>0</v>
       </c>
+      <c r="AP32" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="C33" s="7">
         <v>9.354662980001037E-2</v>
@@ -5252,135 +5352,141 @@
       <c r="AO33" s="7">
         <v>9.354662980001037E-2</v>
       </c>
+      <c r="AP33" s="7">
+        <v>9.354662980001037E-2</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>1</v>
+      </c>
+      <c r="N34" s="4">
+        <v>1</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1</v>
+      </c>
+      <c r="P34" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>1</v>
+      </c>
+      <c r="R34" s="4">
+        <v>1</v>
+      </c>
+      <c r="S34" s="4">
+        <v>1</v>
+      </c>
+      <c r="T34" s="4">
+        <v>1</v>
+      </c>
+      <c r="U34" s="4">
+        <v>1</v>
+      </c>
+      <c r="V34" s="4">
+        <v>1</v>
+      </c>
+      <c r="W34" s="4">
+        <v>1</v>
+      </c>
+      <c r="X34" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>80</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4">
-        <v>1</v>
-      </c>
-      <c r="H34" s="4">
-        <v>1</v>
-      </c>
-      <c r="I34" s="4">
-        <v>1</v>
-      </c>
-      <c r="J34" s="4">
-        <v>1</v>
-      </c>
-      <c r="K34" s="4">
-        <v>1</v>
-      </c>
-      <c r="L34" s="4">
-        <v>1</v>
-      </c>
-      <c r="M34" s="4">
-        <v>1</v>
-      </c>
-      <c r="N34" s="4">
-        <v>1</v>
-      </c>
-      <c r="O34" s="4">
-        <v>1</v>
-      </c>
-      <c r="P34" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>1</v>
-      </c>
-      <c r="R34" s="4">
-        <v>1</v>
-      </c>
-      <c r="S34" s="4">
-        <v>1</v>
-      </c>
-      <c r="T34" s="4">
-        <v>1</v>
-      </c>
-      <c r="U34" s="4">
-        <v>1</v>
-      </c>
-      <c r="V34" s="4">
-        <v>1</v>
-      </c>
-      <c r="W34" s="4">
-        <v>1</v>
-      </c>
-      <c r="X34" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AO34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>81</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>31</v>
@@ -5502,10 +5608,13 @@
       <c r="AO35" s="7">
         <v>4.8164402873198744E-3</v>
       </c>
+      <c r="AP35" s="7">
+        <v>4.8164402873198744E-3</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>33</v>
@@ -5627,10 +5736,13 @@
       <c r="AO36" s="7">
         <v>0.12976890625339038</v>
       </c>
+      <c r="AP36" s="7">
+        <v>0.12976890625339038</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>39</v>
@@ -5752,10 +5864,13 @@
       <c r="AO37" s="7">
         <v>0.22838282599891488</v>
       </c>
+      <c r="AP37" s="7">
+        <v>0.22838282599891488</v>
+      </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>41</v>
@@ -5877,13 +5992,16 @@
       <c r="AO38" s="7">
         <v>3.5767702784609764E-2</v>
       </c>
+      <c r="AP38" s="7">
+        <v>3.5767702784609764E-2</v>
+      </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" s="7">
         <v>0.60126412467576518</v>
@@ -6002,388 +6120,400 @@
       <c r="AO39" s="7">
         <v>0.60126412467576518</v>
       </c>
+      <c r="AP39" s="7">
+        <v>0.60126412467576518</v>
+      </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4">
+        <v>1</v>
+      </c>
+      <c r="I40" s="4">
+        <v>1</v>
+      </c>
+      <c r="J40" s="4">
+        <v>1</v>
+      </c>
+      <c r="K40" s="4">
+        <v>1</v>
+      </c>
+      <c r="L40" s="4">
+        <v>1</v>
+      </c>
+      <c r="M40" s="4">
+        <v>1</v>
+      </c>
+      <c r="N40" s="4">
+        <v>1</v>
+      </c>
+      <c r="O40" s="4">
+        <v>1</v>
+      </c>
+      <c r="P40" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>1</v>
+      </c>
+      <c r="R40" s="4">
+        <v>1</v>
+      </c>
+      <c r="S40" s="4">
+        <v>1</v>
+      </c>
+      <c r="T40" s="4">
+        <v>1</v>
+      </c>
+      <c r="U40" s="4">
+        <v>1</v>
+      </c>
+      <c r="V40" s="4">
+        <v>1</v>
+      </c>
+      <c r="W40" s="4">
+        <v>1</v>
+      </c>
+      <c r="X40" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="4">
-        <v>1</v>
-      </c>
-      <c r="D40" s="4">
-        <v>1</v>
-      </c>
-      <c r="E40" s="4">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4">
-        <v>1</v>
-      </c>
-      <c r="H40" s="4">
-        <v>1</v>
-      </c>
-      <c r="I40" s="4">
-        <v>1</v>
-      </c>
-      <c r="J40" s="4">
-        <v>1</v>
-      </c>
-      <c r="K40" s="4">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4">
-        <v>1</v>
-      </c>
-      <c r="M40" s="4">
-        <v>1</v>
-      </c>
-      <c r="N40" s="4">
-        <v>1</v>
-      </c>
-      <c r="O40" s="4">
-        <v>1</v>
-      </c>
-      <c r="P40" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="4">
-        <v>1</v>
-      </c>
-      <c r="R40" s="4">
-        <v>1</v>
-      </c>
-      <c r="S40" s="4">
-        <v>1</v>
-      </c>
-      <c r="T40" s="4">
-        <v>1</v>
-      </c>
-      <c r="U40" s="4">
-        <v>1</v>
-      </c>
-      <c r="V40" s="4">
-        <v>1</v>
-      </c>
-      <c r="W40" s="4">
-        <v>1</v>
-      </c>
-      <c r="X40" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AI40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AL40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AN40" s="4">
-        <v>1</v>
-      </c>
-      <c r="AO40" s="4">
+      <c r="B41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="11">
+        <v>1</v>
+      </c>
+      <c r="D41" s="11">
+        <v>1</v>
+      </c>
+      <c r="E41" s="11">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11">
+        <v>1</v>
+      </c>
+      <c r="G41" s="11">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11">
+        <v>1</v>
+      </c>
+      <c r="I41" s="11">
+        <v>1</v>
+      </c>
+      <c r="J41" s="11">
+        <v>1</v>
+      </c>
+      <c r="K41" s="11">
+        <v>1</v>
+      </c>
+      <c r="L41" s="11">
+        <v>1</v>
+      </c>
+      <c r="M41" s="11">
+        <v>1</v>
+      </c>
+      <c r="N41" s="11">
+        <v>1</v>
+      </c>
+      <c r="O41" s="11">
+        <v>1</v>
+      </c>
+      <c r="P41" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>1</v>
+      </c>
+      <c r="R41" s="11">
+        <v>1</v>
+      </c>
+      <c r="S41" s="11">
+        <v>1</v>
+      </c>
+      <c r="T41" s="11">
+        <v>1</v>
+      </c>
+      <c r="U41" s="11">
+        <v>1</v>
+      </c>
+      <c r="V41" s="11">
+        <v>1</v>
+      </c>
+      <c r="W41" s="11">
+        <v>1</v>
+      </c>
+      <c r="X41" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AM41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="11">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="11">
-        <v>1</v>
-      </c>
-      <c r="D41" s="11">
-        <v>1</v>
-      </c>
-      <c r="E41" s="11">
-        <v>1</v>
-      </c>
-      <c r="F41" s="11">
-        <v>1</v>
-      </c>
-      <c r="G41" s="11">
-        <v>1</v>
-      </c>
-      <c r="H41" s="11">
-        <v>1</v>
-      </c>
-      <c r="I41" s="11">
-        <v>1</v>
-      </c>
-      <c r="J41" s="11">
-        <v>1</v>
-      </c>
-      <c r="K41" s="11">
-        <v>1</v>
-      </c>
-      <c r="L41" s="11">
-        <v>1</v>
-      </c>
-      <c r="M41" s="11">
-        <v>1</v>
-      </c>
-      <c r="N41" s="11">
-        <v>1</v>
-      </c>
-      <c r="O41" s="11">
-        <v>1</v>
-      </c>
-      <c r="P41" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="11">
-        <v>1</v>
-      </c>
-      <c r="R41" s="11">
-        <v>1</v>
-      </c>
-      <c r="S41" s="11">
-        <v>1</v>
-      </c>
-      <c r="T41" s="11">
-        <v>1</v>
-      </c>
-      <c r="U41" s="11">
-        <v>1</v>
-      </c>
-      <c r="V41" s="11">
-        <v>1</v>
-      </c>
-      <c r="W41" s="11">
-        <v>1</v>
-      </c>
-      <c r="X41" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AL41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AM41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AN41" s="11">
-        <v>1</v>
-      </c>
-      <c r="AO41" s="11">
+      <c r="B42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1</v>
+      </c>
+      <c r="I42" s="4">
+        <v>1</v>
+      </c>
+      <c r="J42" s="4">
+        <v>1</v>
+      </c>
+      <c r="K42" s="4">
+        <v>1</v>
+      </c>
+      <c r="L42" s="4">
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>1</v>
+      </c>
+      <c r="N42" s="4">
+        <v>1</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1</v>
+      </c>
+      <c r="P42" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>1</v>
+      </c>
+      <c r="R42" s="4">
+        <v>1</v>
+      </c>
+      <c r="S42" s="4">
+        <v>1</v>
+      </c>
+      <c r="T42" s="4">
+        <v>1</v>
+      </c>
+      <c r="U42" s="4">
+        <v>1</v>
+      </c>
+      <c r="V42" s="4">
+        <v>1</v>
+      </c>
+      <c r="W42" s="4">
+        <v>1</v>
+      </c>
+      <c r="X42" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="3" t="s">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="4">
-        <v>1</v>
-      </c>
-      <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="4">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4">
-        <v>1</v>
-      </c>
-      <c r="G42" s="4">
-        <v>1</v>
-      </c>
-      <c r="H42" s="4">
-        <v>1</v>
-      </c>
-      <c r="I42" s="4">
-        <v>1</v>
-      </c>
-      <c r="J42" s="4">
-        <v>1</v>
-      </c>
-      <c r="K42" s="4">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4">
-        <v>1</v>
-      </c>
-      <c r="M42" s="4">
-        <v>1</v>
-      </c>
-      <c r="N42" s="4">
-        <v>1</v>
-      </c>
-      <c r="O42" s="4">
-        <v>1</v>
-      </c>
-      <c r="P42" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="4">
-        <v>1</v>
-      </c>
-      <c r="R42" s="4">
-        <v>1</v>
-      </c>
-      <c r="S42" s="4">
-        <v>1</v>
-      </c>
-      <c r="T42" s="4">
-        <v>1</v>
-      </c>
-      <c r="U42" s="4">
-        <v>1</v>
-      </c>
-      <c r="V42" s="4">
-        <v>1</v>
-      </c>
-      <c r="W42" s="4">
-        <v>1</v>
-      </c>
-      <c r="X42" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AN42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AO42" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>91</v>
-      </c>
       <c r="B43" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C43" s="11">
         <v>1</v>
@@ -6500,6 +6630,9 @@
         <v>1</v>
       </c>
       <c r="AO43" s="11">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="11">
         <v>1</v>
       </c>
     </row>

--- a/database/15-RES_hh_tes.xlsx
+++ b/database/15-RES_hh_tes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\git\buildings\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnalia365-my.sharepoint.com/personal/nekane_hermoso_tecnalia_com/Documents/Documentos/Proyectos/iDesignRES/Enerkad/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F307CB3-BEE7-4E23-8878-A789A31470E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{4489598F-76F7-42DF-999A-4E2430255BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE027D53-0A8D-49B2-B55B-2F7252D1BCF8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3CA8CBF-D0C1-4D06-993D-3A172832AF0F}"/>
   </bookViews>
@@ -460,9 +460,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0000;\-#,##0.0000;&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -619,13 +620,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -658,9 +660,9 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Millares 2" xfId="4" xr:uid="{F28AAB3B-FCD3-4C1C-B802-9FEF6664C270}"/>
     <cellStyle name="Millares 3" xfId="3" xr:uid="{9D330414-D2A3-4933-A75C-3C8A364275F6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 3" xfId="2" xr:uid="{DEB7684A-21E2-4BE2-9977-BA735B633DA8}"/>
@@ -677,81 +679,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="CuadroTexto 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BC24CC1-0978-4417-8771-1ADCB8163CED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5173980" y="2065020"/>
-          <a:ext cx="2308860" cy="1005840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1100"/>
-            <a:t>He metido estos 3 combustibles nuevos para que haya la posibilidad de incluirlos en los shares de escenarios futuros</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,7 +1054,7 @@
   <dimension ref="A1:AP43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="47.140625" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
   </cols>
@@ -1396,100 +1323,100 @@
         <v>31</v>
       </c>
       <c r="C3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="D3" s="7">
-        <v>1.752345701426696E-3</v>
+        <v>1.3667082200778116E-3</v>
       </c>
       <c r="E3" s="7">
-        <v>6.065086305324977E-3</v>
+        <v>4.6237218612986391E-3</v>
       </c>
       <c r="F3" s="7">
-        <v>9.8535800346661803E-2</v>
+        <v>1.2850584027882259E-2</v>
       </c>
       <c r="G3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="H3" s="7">
         <v>0</v>
       </c>
       <c r="I3" s="7">
-        <v>9.3507822806232557E-2</v>
+        <v>7.8366236897162767E-2</v>
       </c>
       <c r="J3" s="7">
-        <v>8.3704249809133241E-3</v>
+        <v>8.6336268169105532E-3</v>
       </c>
       <c r="K3" s="7">
         <v>0</v>
       </c>
       <c r="L3" s="7">
-        <v>6.5627944144976895E-4</v>
+        <v>3.4564815538275115E-4</v>
       </c>
       <c r="M3" s="7">
-        <v>1.2758676727669495E-3</v>
+        <v>0</v>
       </c>
       <c r="N3" s="7">
-        <v>2.5999999999999999E-3</v>
+        <v>1.0545798450764903E-2</v>
       </c>
       <c r="O3" s="7">
-        <v>6.976997727529715E-4</v>
+        <v>6.3834442703521828E-4</v>
       </c>
       <c r="P3" s="7">
-        <v>7.6106289951097966E-4</v>
+        <v>7.3729257168586885E-4</v>
       </c>
       <c r="Q3" s="7">
-        <v>9.4788976967769478E-4</v>
+        <v>6.394127823719577E-4</v>
       </c>
       <c r="R3" s="7">
-        <v>9.1471540951738352E-3</v>
+        <v>7.9348957004736903E-3</v>
       </c>
       <c r="S3" s="7">
-        <v>0.1422429501587435</v>
+        <v>0.11520560448480606</v>
       </c>
       <c r="T3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="U3" s="7">
         <v>0</v>
       </c>
       <c r="V3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="W3" s="7">
-        <v>2.7503917717871966E-2</v>
+        <v>1.4566262774718E-2</v>
       </c>
       <c r="X3" s="7">
-        <v>9.2193516264247829E-4</v>
+        <v>6.961648001644901E-4</v>
       </c>
       <c r="Y3" s="7">
-        <v>1.1251630054661926E-3</v>
+        <v>1.1645248871070351E-3</v>
       </c>
       <c r="Z3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AA3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AB3" s="7">
         <v>0</v>
       </c>
       <c r="AC3" s="7">
-        <v>4.9629103008177084E-5</v>
+        <v>1.0603401785217316E-5</v>
       </c>
       <c r="AD3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AE3" s="7">
-        <v>0.24155612456058925</v>
+        <v>0.22515280133496657</v>
       </c>
       <c r="AF3" s="7">
         <v>0</v>
       </c>
       <c r="AG3" s="7">
-        <v>5.7927516337648362E-3</v>
+        <v>8.3863690968283503E-3</v>
       </c>
       <c r="AH3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AI3" s="7">
         <v>0</v>
@@ -1498,22 +1425,22 @@
         <v>0</v>
       </c>
       <c r="AK3" s="7">
-        <v>2.2247563096528009E-2</v>
+        <v>1.6053091977504316E-2</v>
       </c>
       <c r="AL3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AM3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AN3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AO3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
       <c r="AP3" s="7">
-        <v>3.0240676427477773E-2</v>
+        <v>2.8008932275490554E-2</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
@@ -1524,124 +1451,124 @@
         <v>33</v>
       </c>
       <c r="C4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="D4" s="7">
-        <v>4.503384633017235E-3</v>
+        <v>4.136373219161763E-3</v>
       </c>
       <c r="E4" s="7">
-        <v>2.0172695215616734E-2</v>
+        <v>1.9802170182113703E-2</v>
       </c>
       <c r="F4" s="7">
-        <v>3.7716646727076214E-4</v>
+        <v>3.0153274941086819E-4</v>
       </c>
       <c r="G4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="H4" s="7">
-        <v>0.10456191829217397</v>
+        <v>0.1180145531613819</v>
       </c>
       <c r="I4" s="7">
-        <v>7.9123098724705587E-3</v>
+        <v>1.090081752812337E-2</v>
       </c>
       <c r="J4" s="7">
-        <v>1.5017735837357092E-2</v>
+        <v>1.15010910084993E-2</v>
       </c>
       <c r="K4" s="7">
-        <v>3.134695905485312E-3</v>
+        <v>3.8171032500698247E-3</v>
       </c>
       <c r="L4" s="7">
         <v>0</v>
       </c>
       <c r="M4" s="7">
-        <v>1.2899114711131889E-2</v>
+        <v>2.2780800058118628E-2</v>
       </c>
       <c r="N4" s="7">
-        <v>2E-3</v>
+        <v>4.192348621610574E-2</v>
       </c>
       <c r="O4" s="7">
         <v>0</v>
       </c>
       <c r="P4" s="7">
-        <v>1.2333942747166737E-2</v>
+        <v>9.7280580835930486E-3</v>
       </c>
       <c r="Q4" s="7">
-        <v>2.3222428219127184E-3</v>
+        <v>2.003553761354753E-3</v>
       </c>
       <c r="R4" s="7">
-        <v>3.9709879382762448E-4</v>
+        <v>4.1012258726543215E-4</v>
       </c>
       <c r="S4" s="7">
-        <v>1.6463141309570283E-2</v>
+        <v>2.1167838298531999E-2</v>
       </c>
       <c r="T4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="U4" s="7">
-        <v>3.0251665003663188E-2</v>
+        <v>3.0014534809349271E-2</v>
       </c>
       <c r="V4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="W4" s="7">
-        <v>1.2464955854464433E-3</v>
+        <v>2.1044129119139657E-3</v>
       </c>
       <c r="X4" s="7">
-        <v>7.5881124864359752E-5</v>
+        <v>5.0352532605142777E-5</v>
       </c>
       <c r="Y4" s="7">
-        <v>1.4630874677986716E-3</v>
+        <v>2.8883646712092922E-3</v>
       </c>
       <c r="Z4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AA4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AB4" s="7">
-        <v>4.9940318125184104E-2</v>
+        <v>4.2368563257184071E-2</v>
       </c>
       <c r="AC4" s="7">
-        <v>2.7375890212958287E-3</v>
+        <v>3.6855544488443672E-3</v>
       </c>
       <c r="AD4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AE4" s="7">
-        <v>1.1162181549610628E-3</v>
+        <v>1.6797618188945018E-3</v>
       </c>
       <c r="AF4" s="7">
-        <v>1.3951206372500581E-2</v>
+        <v>1.11774929056559E-2</v>
       </c>
       <c r="AG4" s="7">
-        <v>5.5168810558111351E-5</v>
+        <v>6.244222967412478E-5</v>
       </c>
       <c r="AH4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AI4" s="7">
-        <v>3.2530259914043163E-4</v>
+        <v>2.9859927826074982E-4</v>
       </c>
       <c r="AJ4" s="7">
-        <v>1.2596282461350737E-2</v>
+        <v>1.4053572640345145E-2</v>
       </c>
       <c r="AK4" s="7">
-        <v>1.9027149494741573E-3</v>
+        <v>7.5620495902377067E-4</v>
       </c>
       <c r="AL4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AM4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AN4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AO4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
       <c r="AP4" s="7">
-        <v>1.2518193117781035E-2</v>
+        <v>1.1683874731901304E-2</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
@@ -1652,124 +1579,124 @@
         <v>35</v>
       </c>
       <c r="C5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="D5" s="7">
-        <v>0.1262108080688662</v>
+        <v>9.9411379569792249E-2</v>
       </c>
       <c r="E5" s="7">
-        <v>0.30526145211248817</v>
+        <v>0.26663692473296446</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
       </c>
       <c r="G5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="H5" s="7">
-        <v>0.36728230080701407</v>
+        <v>0.37578550989687171</v>
       </c>
       <c r="I5" s="7">
         <v>0</v>
       </c>
       <c r="J5" s="7">
-        <v>0.12767399160162615</v>
+        <v>0.18538070959263839</v>
       </c>
       <c r="K5" s="7">
-        <v>2.7178830084106161E-2</v>
+        <v>2.7679797242547398E-2</v>
       </c>
       <c r="L5" s="7">
-        <v>9.6171062829761972E-4</v>
+        <v>9.4992652028817021E-4</v>
       </c>
       <c r="M5" s="7">
-        <v>0.35914066773768261</v>
+        <v>0.30847577166454099</v>
       </c>
       <c r="N5" s="7">
-        <v>0.1303</v>
+        <v>0.15920346564317817</v>
       </c>
       <c r="O5" s="7">
-        <v>4.945128235774434E-2</v>
+        <v>3.542980690830675E-2</v>
       </c>
       <c r="P5" s="7">
-        <v>7.9836461830059421E-2</v>
+        <v>7.2301685791461207E-2</v>
       </c>
       <c r="Q5" s="7">
-        <v>2.0520366703983779E-2</v>
+        <v>2.8086494030828663E-2</v>
       </c>
       <c r="R5" s="7">
         <v>0</v>
       </c>
       <c r="S5" s="7">
-        <v>0.45012063793456286</v>
+        <v>0.44830484197821552</v>
       </c>
       <c r="T5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="U5" s="7">
-        <v>2.3340821855220264E-2</v>
+        <v>1.867041187852591E-2</v>
       </c>
       <c r="V5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="W5" s="7">
-        <v>1.6651670700378752E-2</v>
+        <v>2.0064606252691672E-2</v>
       </c>
       <c r="X5" s="7">
-        <v>0.29643796573846287</v>
+        <v>0.31727412422166318</v>
       </c>
       <c r="Y5" s="7">
-        <v>2.9190059859224234E-2</v>
+        <v>3.3696338222682504E-2</v>
       </c>
       <c r="Z5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AA5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AB5" s="7">
-        <v>7.0957536447821936E-4</v>
+        <v>4.8496797125545908E-4</v>
       </c>
       <c r="AC5" s="7">
-        <v>1.4161616162234887E-3</v>
+        <v>5.4885482599245326E-3</v>
       </c>
       <c r="AD5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AE5" s="7">
-        <v>4.7479084052297919E-3</v>
+        <v>4.3131196221927459E-3</v>
       </c>
       <c r="AF5" s="7">
-        <v>2.4982542082879804E-2</v>
+        <v>1.7691347772246194E-2</v>
       </c>
       <c r="AG5" s="7">
-        <v>5.8816853004745101E-3</v>
+        <v>7.2251028302829307E-3</v>
       </c>
       <c r="AH5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AI5" s="7">
-        <v>2.166013047958127E-2</v>
+        <v>1.2926039646904678E-2</v>
       </c>
       <c r="AJ5" s="7">
-        <v>8.5796416140456272E-2</v>
+        <v>0.10456581795959879</v>
       </c>
       <c r="AK5" s="7">
         <v>0</v>
       </c>
       <c r="AL5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AM5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AN5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AO5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
       <c r="AP5" s="7">
-        <v>8.0664870072846784E-2</v>
+        <v>8.8453562899217103E-2</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
@@ -1908,124 +1835,124 @@
         <v>39</v>
       </c>
       <c r="C7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="D7" s="7">
-        <v>0.23530476234457567</v>
+        <v>0.20887611103423859</v>
       </c>
       <c r="E7" s="7">
-        <v>0.49236660954976219</v>
+        <v>0.48446505435319093</v>
       </c>
       <c r="F7" s="7">
-        <v>7.4260563721455522E-2</v>
+        <v>5.79493088639104E-2</v>
       </c>
       <c r="G7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
       </c>
       <c r="I7" s="7">
-        <v>0.28206963814177605</v>
+        <v>0.24219071117737592</v>
       </c>
       <c r="J7" s="7">
-        <v>0.52291105802497762</v>
+        <v>0.43488170747486432</v>
       </c>
       <c r="K7" s="7">
-        <v>0.13859104765768129</v>
+        <v>7.0189244179552676E-2</v>
       </c>
       <c r="L7" s="7">
-        <v>6.8333664795882557E-2</v>
+        <v>6.1258515182978923E-2</v>
       </c>
       <c r="M7" s="7">
-        <v>0.20906453222068019</v>
+        <v>0.17551614279001174</v>
       </c>
       <c r="N7" s="7">
-        <v>0.77529999999999999</v>
+        <v>0.28781046769851037</v>
       </c>
       <c r="O7" s="7">
-        <v>4.6163912914838831E-3</v>
+        <v>1.536958698599507E-3</v>
       </c>
       <c r="P7" s="7">
-        <v>0.31894593060823379</v>
+        <v>0.26048423852787783</v>
       </c>
       <c r="Q7" s="7">
-        <v>0.25546249517782055</v>
+        <v>0.25598517827875589</v>
       </c>
       <c r="R7" s="7">
-        <v>0.60642200645264854</v>
+        <v>0.5300070035599953</v>
       </c>
       <c r="S7" s="7">
-        <v>0.22876005401090779</v>
+        <v>0.21996271997747119</v>
       </c>
       <c r="T7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="U7" s="7">
-        <v>0.56604889099113365</v>
+        <v>0.53355296261711549</v>
       </c>
       <c r="V7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="W7" s="7">
-        <v>0.14769100957152198</v>
+        <v>0.12550908075562903</v>
       </c>
       <c r="X7" s="7">
-        <v>0.59103619783471406</v>
+        <v>0.51991971945224935</v>
       </c>
       <c r="Y7" s="7">
-        <v>0.1018264422344988</v>
+        <v>8.2591845182304308E-2</v>
       </c>
       <c r="Z7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AA7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AB7" s="7">
         <v>0</v>
       </c>
       <c r="AC7" s="7">
-        <v>0.83814473849083759</v>
+        <v>0.74105756552561663</v>
       </c>
       <c r="AD7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AE7" s="7">
-        <v>0.22615101623325334</v>
+        <v>0.23215383442778578</v>
       </c>
       <c r="AF7" s="7">
-        <v>0.11668219769954558</v>
+        <v>9.7115133423155739E-2</v>
       </c>
       <c r="AG7" s="7">
-        <v>0.42305249815804324</v>
+        <v>0.39069087920349277</v>
       </c>
       <c r="AH7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AI7" s="7">
-        <v>2.8190764364575791E-3</v>
+        <v>2.2306208457420046E-3</v>
       </c>
       <c r="AJ7" s="7">
-        <v>0.11451666723329741</v>
+        <v>9.2902188401691996E-2</v>
       </c>
       <c r="AK7" s="7">
-        <v>0.45691084474416421</v>
+        <v>0.46883156956235583</v>
       </c>
       <c r="AL7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AM7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AN7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AO7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
       <c r="AP7" s="7">
-        <v>0.38580352338530277</v>
+        <v>0.33426133457280138</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
@@ -2036,124 +1963,124 @@
         <v>41</v>
       </c>
       <c r="C8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="D8" s="7">
-        <v>0.30946105126302714</v>
+        <v>0.30799649055861344</v>
       </c>
       <c r="E8" s="7">
-        <v>9.8167296659461264E-2</v>
+        <v>0.11699345523040712</v>
       </c>
       <c r="F8" s="7">
-        <v>0.5095196233634095</v>
+        <v>0.53480526211046231</v>
       </c>
       <c r="G8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="H8" s="7">
-        <v>0.1487730493120851</v>
+        <v>0.15684999442089695</v>
       </c>
       <c r="I8" s="7">
-        <v>0.33494371870564543</v>
+        <v>0.34702964086672322</v>
       </c>
       <c r="J8" s="7">
-        <v>0.15151417348040452</v>
+        <v>0.14479599304720214</v>
       </c>
       <c r="K8" s="7">
-        <v>0.19959856998869199</v>
+        <v>0.18661421462554181</v>
       </c>
       <c r="L8" s="7">
-        <v>0.42843992724162422</v>
+        <v>0.42294014815423442</v>
       </c>
       <c r="M8" s="7">
-        <v>0.24869637092947097</v>
+        <v>0.35188866882747405</v>
       </c>
       <c r="N8" s="7">
-        <v>1.18E-2</v>
+        <v>0.24445118795485571</v>
       </c>
       <c r="O8" s="7">
-        <v>0.22004179896827605</v>
+        <v>0.21183095791268791</v>
       </c>
       <c r="P8" s="7">
-        <v>0.21485401830001</v>
+        <v>0.22479387696574799</v>
       </c>
       <c r="Q8" s="7">
-        <v>0.60333358373596657</v>
+        <v>0.58969854959616586</v>
       </c>
       <c r="R8" s="7">
-        <v>0.25241036787110688</v>
+        <v>0.3009111763588983</v>
       </c>
       <c r="S8" s="7">
-        <v>1.0024850277233483E-2</v>
+        <v>1.2184203158473709E-2</v>
       </c>
       <c r="T8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="U8" s="7">
-        <v>0.28349801432969074</v>
+        <v>0.28728058187559669</v>
       </c>
       <c r="V8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="W8" s="7">
-        <v>0.29785137754198732</v>
+        <v>0.28621379326042423</v>
       </c>
       <c r="X8" s="7">
-        <v>3.8394141007524453E-2</v>
+        <v>7.6183596851284674E-2</v>
       </c>
       <c r="Y8" s="7">
-        <v>0.40911748037808143</v>
+        <v>0.44460586972643207</v>
       </c>
       <c r="Z8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AA8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AB8" s="7">
-        <v>5.7733336522235841E-2</v>
+        <v>2.5664256405667774E-2</v>
       </c>
       <c r="AC8" s="7">
-        <v>5.0947458786106778E-2</v>
+        <v>6.9772905883193251E-2</v>
       </c>
       <c r="AD8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AE8" s="7">
-        <v>0.24738767584282345</v>
+        <v>0.23989179430791932</v>
       </c>
       <c r="AF8" s="7">
-        <v>0.42286506426823484</v>
+        <v>0.41699909362218823</v>
       </c>
       <c r="AG8" s="7">
-        <v>0.4292109188062731</v>
+        <v>0.46353301142059605</v>
       </c>
       <c r="AH8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AI8" s="7">
-        <v>9.166698481532716E-2</v>
+        <v>9.1100871611161274E-2</v>
       </c>
       <c r="AJ8" s="7">
-        <v>0.50061630636364529</v>
+        <v>0.43906467346921835</v>
       </c>
       <c r="AK8" s="7">
-        <v>0.24334351303883189</v>
+        <v>0.19907493192645359</v>
       </c>
       <c r="AL8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AM8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AN8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AO8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
       <c r="AP8" s="7">
-        <v>0.21710117759245112</v>
+        <v>0.22196225279133283</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
@@ -2164,7 +2091,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
@@ -2176,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="H9" s="7">
         <v>0</v>
@@ -2185,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="7">
-        <v>9.5077468755204681E-4</v>
+        <v>1.0850349221422353E-3</v>
       </c>
       <c r="K9" s="7">
         <v>0</v>
@@ -2197,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="7">
-        <v>1.2284201156824741E-5</v>
+        <v>1.2645370230994635E-5</v>
       </c>
       <c r="O9" s="7">
         <v>0</v>
@@ -2215,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="T9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="U9" s="7">
-        <v>3.7607240189566581E-5</v>
+        <v>3.9659896585794683E-5</v>
       </c>
       <c r="V9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="W9" s="7">
         <v>0</v>
@@ -2233,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="Z9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AA9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AB9" s="7">
         <v>0</v>
@@ -2245,19 +2172,19 @@
         <v>0</v>
       </c>
       <c r="AD9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AE9" s="7">
-        <v>1.2881213340392458E-3</v>
+        <v>1.6133439546227122E-3</v>
       </c>
       <c r="AF9" s="7">
         <v>0</v>
       </c>
       <c r="AG9" s="7">
-        <v>4.9322158277162063E-4</v>
+        <v>8.608130476529997E-5</v>
       </c>
       <c r="AH9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AI9" s="7">
         <v>0</v>
@@ -2269,19 +2196,19 @@
         <v>0</v>
       </c>
       <c r="AL9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AM9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AN9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AO9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
       <c r="AP9" s="7">
-        <v>3.5469885065176189E-4</v>
+        <v>4.153797582584794E-4</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
@@ -2292,124 +2219,124 @@
         <v>45</v>
       </c>
       <c r="C10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="D10" s="7">
-        <v>0.1466127001070934</v>
+        <v>0.14322954965235457</v>
       </c>
       <c r="E10" s="7">
-        <v>2.5727559293576481E-3</v>
+        <v>2.339198780968089E-3</v>
       </c>
       <c r="F10" s="7">
-        <v>0.2195012786379974</v>
+        <v>0.22965864432523292</v>
       </c>
       <c r="G10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="H10" s="7">
         <v>0</v>
       </c>
       <c r="I10" s="7">
-        <v>0.17090846869841786</v>
+        <v>0.15507086060342959</v>
       </c>
       <c r="J10" s="7">
-        <v>9.7388952493888375E-2</v>
+        <v>9.5962450913400346E-2</v>
       </c>
       <c r="K10" s="7">
-        <v>0.48819637403520105</v>
+        <v>0.49778028885379683</v>
       </c>
       <c r="L10" s="7">
-        <v>0.44010823809492017</v>
+        <v>0.45296918074144649</v>
       </c>
       <c r="M10" s="7">
-        <v>1.4042237281558206E-2</v>
+        <v>1.1054291698418074E-2</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="7">
-        <v>0.3257484979219431</v>
+        <v>0.32860201992869997</v>
       </c>
       <c r="P10" s="7">
-        <v>4.8526380801563046E-2</v>
+        <v>4.9225241378064472E-2</v>
       </c>
       <c r="Q10" s="7">
-        <v>7.4311065540741086E-2</v>
+        <v>6.862177650174632E-2</v>
       </c>
       <c r="R10" s="7">
-        <v>0.10136485350525169</v>
+        <v>0.10561986500512351</v>
       </c>
       <c r="S10" s="7">
         <v>0</v>
       </c>
       <c r="T10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="U10" s="7">
-        <v>3.0864393783376833E-2</v>
+        <v>3.0329636294476745E-2</v>
       </c>
       <c r="V10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="W10" s="7">
-        <v>0.40365211146331054</v>
+        <v>0.38819477782552836</v>
       </c>
       <c r="X10" s="7">
         <v>0</v>
       </c>
       <c r="Y10" s="7">
-        <v>0.4459489471228083</v>
+        <v>0.42399696927252889</v>
       </c>
       <c r="Z10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AA10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AB10" s="7">
         <v>0</v>
       </c>
       <c r="AC10" s="7">
-        <v>4.3513544049929138E-2</v>
+        <v>4.4406899847400233E-2</v>
       </c>
       <c r="AD10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AE10" s="7">
-        <v>0.22854334601259596</v>
+        <v>0.21589672363612272</v>
       </c>
       <c r="AF10" s="7">
-        <v>7.4487315703150711E-4</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="7">
-        <v>0.1148091994832415</v>
+        <v>0.10520862397349237</v>
       </c>
       <c r="AH10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AI10" s="7">
-        <v>0.32738771975867625</v>
+        <v>0.35036427496678613</v>
       </c>
       <c r="AJ10" s="7">
-        <v>9.9038782786858057E-2</v>
+        <v>8.9982423333466191E-2</v>
       </c>
       <c r="AK10" s="7">
-        <v>0.17610038265073708</v>
+        <v>0.15002152081190062</v>
       </c>
       <c r="AL10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AM10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AN10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AO10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
       <c r="AP10" s="7">
-        <v>0.11754795563781997</v>
+        <v>0.11836241999341239</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
@@ -2420,124 +2347,124 @@
         <v>47</v>
       </c>
       <c r="C11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="D11" s="7">
-        <v>9.2651525665022549E-2</v>
+        <v>0.10372561788694347</v>
       </c>
       <c r="E11" s="7">
-        <v>4.6369363831491449E-2</v>
+        <v>8.7965792902180914E-2</v>
       </c>
       <c r="F11" s="7">
         <v>0</v>
       </c>
       <c r="G11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="H11" s="7">
-        <v>0.23799948316302719</v>
+        <v>0.24794482521904129</v>
       </c>
       <c r="I11" s="7">
-        <v>7.3335327693729857E-2</v>
+        <v>0.14845904658708475</v>
       </c>
       <c r="J11" s="7">
-        <v>5.9830895537807766E-2</v>
+        <v>8.9273073976397235E-2</v>
       </c>
       <c r="K11" s="7">
-        <v>0.12652178910716458</v>
+        <v>0.16706917334861304</v>
       </c>
       <c r="L11" s="7">
         <v>0</v>
       </c>
       <c r="M11" s="7">
-        <v>8.5283929182133664E-2</v>
+        <v>0.10955033445407572</v>
       </c>
       <c r="N11" s="7">
-        <v>0</v>
+        <v>6.485528015195928E-2</v>
       </c>
       <c r="O11" s="7">
-        <v>0.2237281684296715</v>
+        <v>0.26813442969386514</v>
       </c>
       <c r="P11" s="7">
-        <v>0.20978839050279885</v>
+        <v>0.27583893417414634</v>
       </c>
       <c r="Q11" s="7">
-        <v>2.0495510796868791E-2</v>
+        <v>1.9572098388301339E-2</v>
       </c>
       <c r="R11" s="7">
-        <v>8.8901724339996938E-3</v>
+        <v>1.9029613744791764E-2</v>
       </c>
       <c r="S11" s="7">
-        <v>5.2406179779476279E-2</v>
+        <v>8.1931153211831212E-2</v>
       </c>
       <c r="T11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="U11" s="7">
-        <v>5.2103848871842856E-2</v>
+        <v>7.7949350037629123E-2</v>
       </c>
       <c r="V11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="W11" s="7">
-        <v>9.1430592233768593E-2</v>
+        <v>0.15056068047388899</v>
       </c>
       <c r="X11" s="7">
-        <v>2.7465801242133131E-2</v>
+        <v>3.1700479358385818E-2</v>
       </c>
       <c r="Y11" s="7">
-        <v>6.6509999418513607E-4</v>
+        <v>7.4568061552175323E-4</v>
       </c>
       <c r="Z11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AA11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AB11" s="7">
-        <v>0.66352974254964325</v>
+        <v>0.67049552591414074</v>
       </c>
       <c r="AC11" s="7">
-        <v>4.7642253321865773E-2</v>
+        <v>0.11487616670289642</v>
       </c>
       <c r="AD11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AE11" s="7">
-        <v>4.150654254187721E-2</v>
+        <v>7.2137638338556298E-2</v>
       </c>
       <c r="AF11" s="7">
-        <v>0.41586261527230445</v>
+        <v>0.44144825893776463</v>
       </c>
       <c r="AG11" s="7">
-        <v>0</v>
+        <v>1.9548627265212778E-2</v>
       </c>
       <c r="AH11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AI11" s="7">
-        <v>0.32021477326204106</v>
+        <v>0.34959339294325908</v>
       </c>
       <c r="AJ11" s="7">
-        <v>0.14166703545145762</v>
+        <v>0.1517001485725043</v>
       </c>
       <c r="AK11" s="7">
-        <v>4.8414934429321148E-2</v>
+        <v>0.10184286584518669</v>
       </c>
       <c r="AL11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AM11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AN11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AO11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
       <c r="AP11" s="7">
-        <v>9.9107251170834951E-2</v>
+        <v>0.13643721966567901</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
@@ -2548,124 +2475,124 @@
         <v>49</v>
       </c>
       <c r="C12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="D12" s="7">
-        <v>7.3191764361150907E-2</v>
+        <v>0.12163070816901633</v>
       </c>
       <c r="E12" s="7">
-        <v>1.2082514195734679E-2</v>
+        <v>1.5013652303490106E-3</v>
       </c>
       <c r="F12" s="7">
-        <v>9.0788564671593755E-2</v>
+        <v>0.15816983191587755</v>
       </c>
       <c r="G12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="H12" s="7">
-        <v>0.13611126459872724</v>
+        <v>9.5878396906667177E-2</v>
       </c>
       <c r="I12" s="7">
-        <v>2.8806660735210887E-2</v>
+        <v>1.0309062982271973E-2</v>
       </c>
       <c r="J12" s="7">
-        <v>2.1107406265413113E-3</v>
+        <v>2.4333385482765081E-3</v>
       </c>
       <c r="K12" s="7">
-        <v>1.1333301550612535E-2</v>
+        <v>1.5619120047820952E-3</v>
       </c>
       <c r="L12" s="7">
-        <v>5.5386686370166846E-2</v>
+        <v>5.3142580090589524E-2</v>
       </c>
       <c r="M12" s="7">
-        <v>5.6030884777927024E-2</v>
+        <v>7.8292430147983271E-3</v>
       </c>
       <c r="N12" s="7">
-        <v>7.8E-2</v>
+        <v>0.18114247932036079</v>
       </c>
       <c r="O12" s="7">
-        <v>0.17215498632756182</v>
+        <v>0.14842747024390646</v>
       </c>
       <c r="P12" s="7">
-        <v>0.10486102300503224</v>
+        <v>9.1769146103977559E-2</v>
       </c>
       <c r="Q12" s="7">
-        <v>1.2352519829744814E-2</v>
+        <v>2.5144327898727014E-2</v>
       </c>
       <c r="R12" s="7">
-        <v>6.9081246329529269E-3</v>
+        <v>2.2276886214244077E-2</v>
       </c>
       <c r="S12" s="7">
-        <v>8.568278288828983E-2</v>
+        <v>8.7043313366156602E-2</v>
       </c>
       <c r="T12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="U12" s="7">
-        <v>2.1962521068134356E-4</v>
+        <v>2.8149094036437946E-3</v>
       </c>
       <c r="V12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="W12" s="7">
-        <v>7.4632792899108529E-3</v>
+        <v>6.2769677427246384E-3</v>
       </c>
       <c r="X12" s="7">
-        <v>2.8163609465217825E-2</v>
+        <v>3.3780637984537946E-2</v>
       </c>
       <c r="Y12" s="7">
-        <v>3.8995936960928646E-3</v>
+        <v>3.4915935644583493E-3</v>
       </c>
       <c r="Z12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AA12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AB12" s="7">
-        <v>0.22644698853943482</v>
+        <v>0.25993160972208168</v>
       </c>
       <c r="AC12" s="7">
-        <v>2.428936535724464E-4</v>
+        <v>3.9575752870638851E-4</v>
       </c>
       <c r="AD12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AE12" s="7">
-        <v>2.5985623937369804E-4</v>
+        <v>1.9925175773041922E-4</v>
       </c>
       <c r="AF12" s="7">
-        <v>4.5129321243464081E-4</v>
+        <v>1.1591733492131728E-2</v>
       </c>
       <c r="AG12" s="7">
-        <v>1.8661776531196377E-2</v>
+        <v>3.2582075926968906E-3</v>
       </c>
       <c r="AH12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AI12" s="7">
-        <v>0.2337020947064411</v>
+        <v>0.18915999091080579</v>
       </c>
       <c r="AJ12" s="7">
-        <v>3.7344279756117614E-2</v>
+        <v>9.9944477586211736E-2</v>
       </c>
       <c r="AK12" s="7">
-        <v>3.9946451929682304E-2</v>
+        <v>5.3800589437336253E-2</v>
       </c>
       <c r="AL12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AM12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AN12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AO12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
       <c r="AP12" s="7">
-        <v>4.578659523529565E-2</v>
+        <v>4.4582486839442569E-2</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
@@ -2676,19 +2603,19 @@
         <v>51</v>
       </c>
       <c r="C13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="D13" s="7">
         <v>0</v>
       </c>
       <c r="E13" s="7">
-        <v>0</v>
+        <v>2.1319604633566189E-4</v>
       </c>
       <c r="F13" s="7">
         <v>0</v>
       </c>
       <c r="G13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="H13" s="7">
         <v>0</v>
@@ -2697,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="7">
-        <v>0</v>
+        <v>1.5965413940926038E-5</v>
       </c>
       <c r="K13" s="7">
         <v>0</v>
@@ -2712,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="7">
-        <v>0</v>
+        <v>1.977976944763963E-3</v>
       </c>
       <c r="P13" s="7">
         <v>0</v>
@@ -2727,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="T13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="U13" s="7">
         <v>0</v>
       </c>
       <c r="V13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="W13" s="7">
         <v>0</v>
@@ -2745,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="Z13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AA13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AB13" s="7">
         <v>0</v>
@@ -2757,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AE13" s="7">
         <v>0</v>
@@ -2769,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="AH13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AI13" s="7">
-        <v>0</v>
+        <v>1.9712759471949017E-3</v>
       </c>
       <c r="AJ13" s="7">
         <v>0</v>
@@ -2781,19 +2708,19 @@
         <v>0</v>
       </c>
       <c r="AL13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AM13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AN13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AO13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
       <c r="AP13" s="7">
-        <v>0</v>
+        <v>1.6387079424452382E-4</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
@@ -2804,88 +2731,88 @@
         <v>53</v>
       </c>
       <c r="C14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="D14" s="7">
-        <v>0</v>
+        <v>3.9189458618319243E-4</v>
       </c>
       <c r="E14" s="7">
-        <v>0</v>
+        <v>4.5088380600603862E-4</v>
       </c>
       <c r="F14" s="7">
         <v>0</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="H14" s="7">
         <v>0</v>
       </c>
       <c r="I14" s="7">
-        <v>0</v>
+        <v>9.6887080163501484E-5</v>
       </c>
       <c r="J14" s="7">
-        <v>0</v>
+        <v>1.2149031809712682E-2</v>
       </c>
       <c r="K14" s="7">
-        <v>0</v>
+        <v>4.0493353601070377E-2</v>
       </c>
       <c r="L14" s="7">
-        <v>0</v>
+        <v>2.3891468250449087E-3</v>
       </c>
       <c r="M14" s="7">
         <v>0</v>
       </c>
       <c r="N14" s="7">
-        <v>0</v>
+        <v>2.144276129024949E-4</v>
       </c>
       <c r="O14" s="7">
-        <v>0</v>
+        <v>1.5741024702366045E-5</v>
       </c>
       <c r="P14" s="7">
-        <v>0</v>
+        <v>6.4923978783151511E-3</v>
       </c>
       <c r="Q14" s="7">
         <v>0</v>
       </c>
       <c r="R14" s="7">
-        <v>0</v>
+        <v>6.6604438375747271E-4</v>
       </c>
       <c r="S14" s="7">
-        <v>0</v>
+        <v>2.4668450615491274E-4</v>
       </c>
       <c r="T14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="U14" s="7">
-        <v>0</v>
+        <v>2.5101048893592087E-3</v>
       </c>
       <c r="V14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="W14" s="7">
-        <v>0</v>
+        <v>6.0200947333906578E-4</v>
       </c>
       <c r="X14" s="7">
-        <v>0</v>
+        <v>3.831402406864332E-3</v>
       </c>
       <c r="Y14" s="7">
         <v>0</v>
       </c>
       <c r="Z14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AA14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AB14" s="7">
         <v>0</v>
       </c>
       <c r="AC14" s="7">
-        <v>0</v>
+        <v>8.3625801886870847E-3</v>
       </c>
       <c r="AD14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AE14" s="7">
         <v>0</v>
@@ -2897,10 +2824,10 @@
         <v>0</v>
       </c>
       <c r="AH14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AI14" s="7">
-        <v>0</v>
+        <v>1.3345771789212904E-4</v>
       </c>
       <c r="AJ14" s="7">
         <v>0</v>
@@ -2909,19 +2836,19 @@
         <v>0</v>
       </c>
       <c r="AL14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AM14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AN14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AO14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
       <c r="AP14" s="7">
-        <v>0</v>
+        <v>5.2382613613853827E-3</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
@@ -3060,124 +2987,124 @@
         <v>56</v>
       </c>
       <c r="C16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="D16" s="7">
-        <v>1.0311657855820118E-2</v>
+        <v>9.2351671036187966E-3</v>
       </c>
       <c r="E16" s="7">
-        <v>1.6942226200762654E-2</v>
+        <v>1.5008236874185286E-2</v>
       </c>
       <c r="F16" s="7">
-        <v>7.0170027916110515E-3</v>
+        <v>6.264836007223897E-3</v>
       </c>
       <c r="G16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="H16" s="7">
-        <v>5.2719838269724801E-3</v>
+        <v>5.5267203951412632E-3</v>
       </c>
       <c r="I16" s="7">
-        <v>8.5160533465166357E-3</v>
+        <v>7.5767362776649064E-3</v>
       </c>
       <c r="J16" s="7">
-        <v>1.4231252728931923E-2</v>
+        <v>1.3887976476015593E-2</v>
       </c>
       <c r="K16" s="7">
-        <v>5.4453916710570207E-3</v>
+        <v>4.7949128940262351E-3</v>
       </c>
       <c r="L16" s="7">
-        <v>6.1134934276586336E-3</v>
+        <v>6.004854330034841E-3</v>
       </c>
       <c r="M16" s="7">
-        <v>1.3566395486648539E-2</v>
+        <v>1.2904747492562511E-2</v>
       </c>
       <c r="N16" s="7">
-        <v>0</v>
+        <v>9.8407615811315421E-3</v>
       </c>
       <c r="O16" s="7">
-        <v>3.5611749305663062E-3</v>
+        <v>3.4062942174327704E-3</v>
       </c>
       <c r="P16" s="7">
-        <v>1.0092789305625178E-2</v>
+        <v>8.6291285251305083E-3</v>
       </c>
       <c r="Q16" s="7">
-        <v>1.0254325623283603E-2</v>
+        <v>1.0248608761748334E-2</v>
       </c>
       <c r="R16" s="7">
-        <v>1.4460222215039009E-2</v>
+        <v>1.3144392445450537E-2</v>
       </c>
       <c r="S16" s="7">
-        <v>1.4299403641216268E-2</v>
+        <v>1.3953641018358585E-2</v>
       </c>
       <c r="T16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="U16" s="7">
-        <v>1.3635132714201602E-2</v>
+        <v>1.6837848297718002E-2</v>
       </c>
       <c r="V16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="W16" s="7">
-        <v>6.5095458958036615E-3</v>
+        <v>5.9074085291422372E-3</v>
       </c>
       <c r="X16" s="7">
-        <v>1.7504468424440502E-2</v>
+        <v>1.6563522392245185E-2</v>
       </c>
       <c r="Y16" s="7">
-        <v>6.7641262418445293E-3</v>
+        <v>6.8188138577558489E-3</v>
       </c>
       <c r="Z16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AA16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AB16" s="7">
-        <v>1.6400388990240207E-3</v>
+        <v>1.05507672967012E-3</v>
       </c>
       <c r="AC16" s="7">
-        <v>1.5305731957160779E-2</v>
+        <v>1.1943418212945658E-2</v>
       </c>
       <c r="AD16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AE16" s="7">
-        <v>7.4431906752567747E-3</v>
+        <v>6.9617308012088477E-3</v>
       </c>
       <c r="AF16" s="7">
-        <v>4.4602079350688278E-3</v>
+        <v>3.9769398468574692E-3</v>
       </c>
       <c r="AG16" s="7">
-        <v>2.0427796936766576E-3</v>
+        <v>2.0006550829582874E-3</v>
       </c>
       <c r="AH16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AI16" s="7">
-        <v>2.2239179423352361E-3</v>
+        <v>2.2214761319930567E-3</v>
       </c>
       <c r="AJ16" s="7">
-        <v>8.424229806817056E-3</v>
+        <v>7.7866980369634704E-3</v>
       </c>
       <c r="AK16" s="7">
-        <v>1.1133595161261254E-2</v>
+        <v>9.6192254802388733E-3</v>
       </c>
       <c r="AL16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AM16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AN16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AO16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
       <c r="AP16" s="7">
-        <v>1.0875058509537966E-2</v>
+        <v>1.0430404316834752E-2</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
@@ -3188,121 +3115,121 @@
         <v>58</v>
       </c>
       <c r="C17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="D17" s="4">
-        <v>7.8005171418880526E-2</v>
+        <v>8.0259745368748997E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>6.2041741679588494E-2</v>
+        <v>8.0000091766902884E-2</v>
       </c>
       <c r="F17" s="4">
-        <v>0.45959177309930754</v>
+        <v>0.60999880892580638</v>
       </c>
       <c r="G17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="H17" s="4">
-        <v>0.84043329093391528</v>
+        <v>0.82207864387939422</v>
       </c>
       <c r="I17" s="4">
-        <v>3.8003239441499498E-2</v>
+        <v>4.6999567901390552E-2</v>
       </c>
       <c r="J17" s="4">
-        <v>4.9904360173527257E-2</v>
+        <v>6.5155988354689401E-2</v>
       </c>
       <c r="K17" s="4">
-        <v>5.1749568576678777E-2</v>
+        <v>7.0828965149717121E-2</v>
       </c>
       <c r="L17" s="4">
-        <v>1.126004265572801E-2</v>
+        <v>1.6280885459722606E-2</v>
       </c>
       <c r="M17" s="4">
-        <v>0.40550681867409649</v>
+        <v>0.49233775791455536</v>
       </c>
       <c r="N17" s="4">
-        <v>0.36003071880376869</v>
+        <v>0.36347868436542163</v>
       </c>
       <c r="O17" s="4">
-        <v>0.12927841523142988</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="P17" s="4">
-        <v>0.20537927914602561</v>
+        <v>0.15537169140050722</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.27528112170366442</v>
+        <v>0.20980622537680216</v>
       </c>
       <c r="R17" s="4">
-        <v>0.16575105420637468</v>
+        <v>0.34310828249809455</v>
       </c>
       <c r="S17" s="4">
-        <v>2.279422901857233E-2</v>
+        <v>0.2199994857174854</v>
       </c>
       <c r="T17" s="4">
-        <v>0.19575193429842577</v>
+        <v>3.390432425391967E-2</v>
       </c>
       <c r="U17" s="4">
-        <v>0.48601104985555471</v>
+        <v>0.51100001840297471</v>
       </c>
       <c r="V17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="W17" s="4">
-        <v>1.8899909314639196E-2</v>
+        <v>1.9200326047319763E-2</v>
       </c>
       <c r="X17" s="4">
-        <v>0.31752551083525671</v>
+        <v>0.37324535625931138</v>
       </c>
       <c r="Y17" s="4">
-        <v>1.5398419774209081E-2</v>
+        <v>1.8540999110709597E-2</v>
       </c>
       <c r="Z17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AA17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AB17" s="4">
-        <v>0.60068544600938967</v>
+        <v>0.60790361360111278</v>
       </c>
       <c r="AC17" s="4">
-        <v>0.17738677332447225</v>
+        <v>0.24437903832841898</v>
       </c>
       <c r="AD17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AE17" s="4">
-        <v>3.6963764990472617E-2</v>
+        <v>3.9045309681848196E-2</v>
       </c>
       <c r="AF17" s="4">
-        <v>0.17831264429487534</v>
+        <v>0.18539236238784018</v>
       </c>
       <c r="AG17" s="4">
-        <v>0.15986435642596772</v>
+        <v>0.16660593900939111</v>
       </c>
       <c r="AH17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AI17" s="4">
-        <v>4.1383109466822124E-2</v>
+        <v>4.2514119102519302E-2</v>
       </c>
       <c r="AJ17" s="4">
-        <v>0.3086692195934595</v>
+        <v>0.40803194395860909</v>
       </c>
       <c r="AK17" s="4">
-        <v>0.10842749588897484</v>
+        <v>0.12898923050596722</v>
       </c>
       <c r="AL17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AM17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AN17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AO17" s="4">
-        <v>0.19575193429842577</v>
+        <v>0.21533959949791268</v>
       </c>
       <c r="AP17" s="4">
         <v>0.19575193429842577</v>
@@ -3700,25 +3627,25 @@
         <v>31</v>
       </c>
       <c r="C21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="D21" s="7">
-        <v>5.2561456952945657E-4</v>
+        <v>2.725428799514842E-4</v>
       </c>
       <c r="E21" s="7">
-        <v>2.7166948450196566E-4</v>
+        <v>1.2844115621928664E-4</v>
       </c>
       <c r="F21" s="7">
-        <v>6.239153907392392E-3</v>
+        <v>6.3271694909535273E-4</v>
       </c>
       <c r="G21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="H21" s="7">
         <v>0</v>
       </c>
       <c r="I21" s="7">
-        <v>2.2275380105130829E-2</v>
+        <v>2.2313771057529026E-2</v>
       </c>
       <c r="J21" s="7">
         <v>0</v>
@@ -3727,52 +3654,52 @@
         <v>0</v>
       </c>
       <c r="L21" s="7">
-        <v>6.5400635590273323E-4</v>
+        <v>0</v>
       </c>
       <c r="M21" s="7">
         <v>0</v>
       </c>
       <c r="N21" s="7">
-        <v>2.5999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="O21" s="7">
-        <v>6.9233747555342521E-4</v>
+        <v>6.1818970560653392E-4</v>
       </c>
       <c r="P21" s="7">
-        <v>3.3704975133457145E-4</v>
+        <v>2.0913452245721368E-4</v>
       </c>
       <c r="Q21" s="7">
-        <v>3.6399182947796795E-4</v>
+        <v>2.2006871023452562E-4</v>
       </c>
       <c r="R21" s="7">
         <v>0</v>
       </c>
       <c r="S21" s="7">
-        <v>6.6191460867140325E-2</v>
+        <v>5.2972060630955164E-2</v>
       </c>
       <c r="T21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="U21" s="7">
         <v>0</v>
       </c>
       <c r="V21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="W21" s="7">
-        <v>2.2504866085096158E-2</v>
+        <v>1.2339251879490887E-2</v>
       </c>
       <c r="X21" s="7">
         <v>0</v>
       </c>
       <c r="Y21" s="7">
-        <v>7.7953468482497919E-4</v>
+        <v>7.0463279566258818E-4</v>
       </c>
       <c r="Z21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AA21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AB21" s="7">
         <v>0</v>
@@ -3781,19 +3708,19 @@
         <v>0</v>
       </c>
       <c r="AD21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AE21" s="7">
-        <v>0.20871190670412332</v>
+        <v>0.22276088312103612</v>
       </c>
       <c r="AF21" s="7">
         <v>0</v>
       </c>
       <c r="AG21" s="7">
-        <v>5.7010828870190013E-3</v>
+        <v>8.0674413059205071E-4</v>
       </c>
       <c r="AH21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AI21" s="7">
         <v>0</v>
@@ -3802,22 +3729,22 @@
         <v>0</v>
       </c>
       <c r="AK21" s="7">
-        <v>1.7836050466788531E-2</v>
+        <v>1.1457743286540315E-2</v>
       </c>
       <c r="AL21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AM21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AN21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AO21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
       <c r="AP21" s="7">
-        <v>1.6158596644350313E-2</v>
+        <v>1.4273443060095316E-2</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
@@ -3828,79 +3755,79 @@
         <v>33</v>
       </c>
       <c r="C22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="D22" s="7">
-        <v>3.0838450634148749E-3</v>
+        <v>3.1439507602298118E-3</v>
       </c>
       <c r="E22" s="7">
-        <v>1.6550905261117761E-2</v>
+        <v>2.9032286157332329E-2</v>
       </c>
       <c r="F22" s="7">
-        <v>1.4151801553473017E-3</v>
+        <v>8.2652241874868308E-4</v>
       </c>
       <c r="G22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="H22" s="7">
-        <v>2.2310333738319549E-2</v>
+        <v>2.1649276188649737E-2</v>
       </c>
       <c r="I22" s="7">
         <v>0</v>
       </c>
       <c r="J22" s="7">
-        <v>1.4948853881175542E-2</v>
+        <v>1.1348757680655816E-2</v>
       </c>
       <c r="K22" s="7">
-        <v>2.2250250007567352E-2</v>
+        <v>3.0176204517877264E-2</v>
       </c>
       <c r="L22" s="7">
         <v>0</v>
       </c>
       <c r="M22" s="7">
-        <v>2.1671075215766596E-3</v>
+        <v>2.1730631630434523E-3</v>
       </c>
       <c r="N22" s="7">
-        <v>2E-3</v>
+        <v>0.1992361132827338</v>
       </c>
       <c r="O22" s="7">
         <v>0</v>
       </c>
       <c r="P22" s="7">
-        <v>1.8657086934673668E-2</v>
+        <v>1.3841834552383817E-2</v>
       </c>
       <c r="Q22" s="7">
-        <v>1.6113953347881509E-2</v>
+        <v>1.2337702948634486E-2</v>
       </c>
       <c r="R22" s="7">
-        <v>1.1842837022683898E-2</v>
+        <v>1.0165953450653527E-2</v>
       </c>
       <c r="S22" s="7">
-        <v>2.110809301477121E-2</v>
+        <v>2.7151714037436572E-2</v>
       </c>
       <c r="T22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="U22" s="7">
-        <v>6.6924745392713633E-2</v>
+        <v>9.1488195646885345E-2</v>
       </c>
       <c r="V22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="W22" s="7">
-        <v>2.0808669769421797E-3</v>
+        <v>9.593935346279071E-3</v>
       </c>
       <c r="X22" s="7">
         <v>0</v>
       </c>
       <c r="Y22" s="7">
-        <v>3.1019499811713439E-3</v>
+        <v>6.4443287283469115E-3</v>
       </c>
       <c r="Z22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AA22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AB22" s="7">
         <v>0</v>
@@ -3909,43 +3836,43 @@
         <v>0</v>
       </c>
       <c r="AD22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AE22" s="7">
-        <v>1.2033919158969605E-2</v>
+        <v>1.3426106346956224E-2</v>
       </c>
       <c r="AF22" s="7">
-        <v>0.47993730967867043</v>
+        <v>0.43402237215457024</v>
       </c>
       <c r="AG22" s="7">
-        <v>5.61333105517412E-2</v>
+        <v>6.3817407657969075E-2</v>
       </c>
       <c r="AH22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AI22" s="7">
-        <v>2.3294964167124457E-3</v>
+        <v>3.0133776202627082E-3</v>
       </c>
       <c r="AJ22" s="7">
-        <v>1.9886587874827229E-2</v>
+        <v>2.7965783153512308E-2</v>
       </c>
       <c r="AK22" s="7">
-        <v>1.1254796477088018E-2</v>
+        <v>1.6774972131523087E-2</v>
       </c>
       <c r="AL22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AM22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AN22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AO22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
       <c r="AP22" s="7">
-        <v>3.7376338764954511E-2</v>
+        <v>3.9855567761418666E-2</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
@@ -3956,79 +3883,79 @@
         <v>35</v>
       </c>
       <c r="C23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="D23" s="7">
-        <v>8.1926270856754566E-2</v>
+        <v>6.9200875861509456E-2</v>
       </c>
       <c r="E23" s="7">
-        <v>0.12976133441711277</v>
+        <v>0.16986553275224342</v>
       </c>
       <c r="F23" s="7">
         <v>0</v>
       </c>
       <c r="G23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="H23" s="7">
-        <v>4.1559139314232635E-2</v>
+        <v>3.6858011965558039E-2</v>
       </c>
       <c r="I23" s="7">
         <v>0</v>
       </c>
       <c r="J23" s="7">
-        <v>0.11669222517878715</v>
+        <v>0.17567472766328621</v>
       </c>
       <c r="K23" s="7">
-        <v>2.666958623743905E-2</v>
+        <v>2.4721244091807034E-2</v>
       </c>
       <c r="L23" s="7">
-        <v>9.4116090221646389E-4</v>
+        <v>8.7590021744848791E-4</v>
       </c>
       <c r="M23" s="7">
-        <v>6.402922070923131E-2</v>
+        <v>9.0905445763122539E-2</v>
       </c>
       <c r="N23" s="7">
-        <v>0.1303</v>
+        <v>5.3074236582693196E-2</v>
       </c>
       <c r="O23" s="7">
-        <v>4.8780486521971221E-2</v>
+        <v>2.6515311380971966E-2</v>
       </c>
       <c r="P23" s="7">
-        <v>7.927415905158218E-2</v>
+        <v>6.1913808189006686E-2</v>
       </c>
       <c r="Q23" s="7">
-        <v>9.4380286518649797E-3</v>
+        <v>9.9325285841592639E-3</v>
       </c>
       <c r="R23" s="7">
         <v>0</v>
       </c>
       <c r="S23" s="7">
-        <v>0.44831609512667309</v>
+        <v>0.44624255644752209</v>
       </c>
       <c r="T23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="U23" s="7">
-        <v>2.1506817371520055E-2</v>
+        <v>1.8398550604230606E-2</v>
       </c>
       <c r="V23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="W23" s="7">
-        <v>1.6426638368557872E-2</v>
+        <v>1.9832489071218307E-2</v>
       </c>
       <c r="X23" s="7">
-        <v>0.24777839019443643</v>
+        <v>0.24284975916492296</v>
       </c>
       <c r="Y23" s="7">
-        <v>2.8789087258888384E-2</v>
+        <v>3.3529460829380478E-2</v>
       </c>
       <c r="Z23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AA23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AB23" s="7">
         <v>0</v>
@@ -4037,43 +3964,43 @@
         <v>0</v>
       </c>
       <c r="AD23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AE23" s="7">
-        <v>4.6659352081878614E-3</v>
+        <v>2.7097714969030488E-3</v>
       </c>
       <c r="AF23" s="7">
-        <v>2.3598747208482776E-2</v>
+        <v>1.7016553214567371E-2</v>
       </c>
       <c r="AG23" s="7">
         <v>0</v>
       </c>
       <c r="AH23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AI23" s="7">
-        <v>1.0387286912557241E-2</v>
+        <v>5.6541580874428822E-3</v>
       </c>
       <c r="AJ23" s="7">
-        <v>5.170014197367797E-2</v>
+        <v>7.1056449793586163E-2</v>
       </c>
       <c r="AK23" s="7">
         <v>0</v>
       </c>
       <c r="AL23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AM23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AN23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AO23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
       <c r="AP23" s="7">
-        <v>7.0503295552177631E-2</v>
+        <v>9.0234273248254518E-2</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
@@ -4084,124 +4011,124 @@
         <v>39</v>
       </c>
       <c r="C24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="D24" s="7">
-        <v>0.17638817124115291</v>
+        <v>0.13546307645474656</v>
       </c>
       <c r="E24" s="7">
-        <v>0.49355135564890046</v>
+        <v>0.44803592641050466</v>
       </c>
       <c r="F24" s="7">
-        <v>3.801947198629578E-2</v>
+        <v>2.9916914708316648E-2</v>
       </c>
       <c r="G24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="H24" s="7">
         <v>0</v>
       </c>
       <c r="I24" s="7">
-        <v>0.27839823251444856</v>
+        <v>0.23998789664425796</v>
       </c>
       <c r="J24" s="7">
-        <v>0.50059601183061486</v>
+        <v>0.42140162507010398</v>
       </c>
       <c r="K24" s="7">
-        <v>0.13630063327655997</v>
+        <v>6.8685380025674661E-2</v>
       </c>
       <c r="L24" s="7">
-        <v>6.7419931721108911E-2</v>
+        <v>5.9469276144445804E-2</v>
       </c>
       <c r="M24" s="7">
-        <v>2.1413826382892773E-2</v>
+        <v>2.3973980687889137E-2</v>
       </c>
       <c r="N24" s="7">
-        <v>0.77529999999999999</v>
+        <v>0.28352471992068834</v>
       </c>
       <c r="O24" s="7">
-        <v>4.5531009049518262E-3</v>
+        <v>1.4854387538513814E-3</v>
       </c>
       <c r="P24" s="7">
-        <v>0.29484404947649168</v>
+        <v>0.26212922937246724</v>
       </c>
       <c r="Q24" s="7">
-        <v>0.25361688129048299</v>
+        <v>0.23848328718306466</v>
       </c>
       <c r="R24" s="7">
-        <v>0.45840132741845424</v>
+        <v>0.46380357750312318</v>
       </c>
       <c r="S24" s="7">
-        <v>0.22761509327790619</v>
+        <v>0.21908921253785962</v>
       </c>
       <c r="T24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="U24" s="7">
-        <v>0.56201835447829029</v>
+        <v>0.52589581710435573</v>
       </c>
       <c r="V24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="W24" s="7">
-        <v>0.14568030441473059</v>
+        <v>0.12415407436601061</v>
       </c>
       <c r="X24" s="7">
-        <v>0.52505970658482293</v>
+        <v>0.47104834417183139</v>
       </c>
       <c r="Y24" s="7">
-        <v>0.10043677432414383</v>
+        <v>8.2141678504808247E-2</v>
       </c>
       <c r="Z24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AA24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AB24" s="7">
         <v>0</v>
       </c>
       <c r="AC24" s="7">
-        <v>0.84160776093903533</v>
+        <v>0.74515073636845763</v>
       </c>
       <c r="AD24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AE24" s="7">
-        <v>0.22247328550367756</v>
+        <v>0.22416477209609742</v>
       </c>
       <c r="AF24" s="7">
-        <v>0.11013135762480442</v>
+        <v>9.3227311477997565E-2</v>
       </c>
       <c r="AG24" s="7">
-        <v>0.41501546671056067</v>
+        <v>0.38564805523643753</v>
       </c>
       <c r="AH24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AI24" s="7">
-        <v>2.7719232257558059E-3</v>
+        <v>2.1954256060762274E-3</v>
       </c>
       <c r="AJ24" s="7">
-        <v>0.10998874071664547</v>
+        <v>9.2064292298322831E-2</v>
       </c>
       <c r="AK24" s="7">
-        <v>0.36091648848940738</v>
+        <v>0.47025806325837005</v>
       </c>
       <c r="AL24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AM24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AN24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AO24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
       <c r="AP24" s="7">
-        <v>0.37586071948258948</v>
+        <v>0.32576371691360134</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
@@ -4212,79 +4139,79 @@
         <v>41</v>
       </c>
       <c r="C25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="D25" s="7">
-        <v>0.17693663499499157</v>
+        <v>0.14720252476682844</v>
       </c>
       <c r="E25" s="7">
-        <v>4.3996336537635433E-3</v>
+        <v>1.8028216566477118E-2</v>
       </c>
       <c r="F25" s="7">
-        <v>4.1479303862805697E-2</v>
+        <v>3.07580503358666E-2</v>
       </c>
       <c r="G25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="H25" s="7">
-        <v>1.4179271901434945E-3</v>
+        <v>1.0435675615196719E-3</v>
       </c>
       <c r="I25" s="7">
-        <v>0.13673004230500399</v>
+        <v>0.1589226362661908</v>
       </c>
       <c r="J25" s="7">
-        <v>9.1938931983304967E-2</v>
+        <v>8.8164055218075632E-2</v>
       </c>
       <c r="K25" s="7">
-        <v>0.16805900641256946</v>
+        <v>0.16779980427868579</v>
       </c>
       <c r="L25" s="7">
-        <v>0.40370049047358081</v>
+        <v>0.40207086017600069</v>
       </c>
       <c r="M25" s="7">
-        <v>1.5743317560127774E-2</v>
+        <v>1.7407416390253467E-2</v>
       </c>
       <c r="N25" s="7">
-        <v>1.18E-2</v>
+        <v>1.9558747824694783E-2</v>
       </c>
       <c r="O25" s="7">
-        <v>9.0833911348612531E-2</v>
+        <v>9.1595851477248469E-2</v>
       </c>
       <c r="P25" s="7">
-        <v>9.8966970498307796E-3</v>
+        <v>2.1136816280925976E-2</v>
       </c>
       <c r="Q25" s="7">
-        <v>7.4469058010136244E-2</v>
+        <v>0.11881064882247351</v>
       </c>
       <c r="R25" s="7">
-        <v>1.8523648599334631E-2</v>
+        <v>1.7787921986341371E-2</v>
       </c>
       <c r="S25" s="7">
-        <v>8.6021093269000627E-3</v>
+        <v>1.124916904143237E-2</v>
       </c>
       <c r="T25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="U25" s="7">
-        <v>8.610002969085255E-2</v>
+        <v>0.10829523761470136</v>
       </c>
       <c r="V25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="W25" s="7">
-        <v>0.24314529721906877</v>
+        <v>0.28327059751161132</v>
       </c>
       <c r="X25" s="7">
-        <v>3.474165524352061E-2</v>
+        <v>4.0477739865464366E-2</v>
       </c>
       <c r="Y25" s="7">
-        <v>0.29700575596153611</v>
+        <v>0.33088134765422095</v>
       </c>
       <c r="Z25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AA25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AB25" s="7">
         <v>0</v>
@@ -4293,43 +4220,43 @@
         <v>0</v>
       </c>
       <c r="AD25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AE25" s="7">
-        <v>0.21166724344609714</v>
+        <v>0.23202573728293777</v>
       </c>
       <c r="AF25" s="7">
-        <v>0.12866897345615322</v>
+        <v>0.13820816320191809</v>
       </c>
       <c r="AG25" s="7">
-        <v>0.37057269335725002</v>
+        <v>0.39465437037837486</v>
       </c>
       <c r="AH25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AI25" s="7">
-        <v>9.0193728197828907E-2</v>
+        <v>8.794762671117691E-2</v>
       </c>
       <c r="AJ25" s="7">
-        <v>0.28808927704172277</v>
+        <v>0.24880897223197246</v>
       </c>
       <c r="AK25" s="7">
-        <v>0.1874613285011402</v>
+        <v>0.14486427214482722</v>
       </c>
       <c r="AL25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AM25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AN25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AO25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
       <c r="AP25" s="7">
-        <v>9.1410335212849164E-2</v>
+        <v>9.6214151795856781E-2</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
@@ -4340,7 +4267,7 @@
         <v>43</v>
       </c>
       <c r="C26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
@@ -4352,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="H26" s="7">
         <v>0</v>
@@ -4361,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="7">
-        <v>4.055423818229108E-4</v>
+        <v>4.4364036812806934E-4</v>
       </c>
       <c r="K26" s="7">
         <v>0</v>
@@ -4373,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="7">
-        <v>1.2284201156824741E-5</v>
+        <v>7.8866939518742905E-6</v>
       </c>
       <c r="O26" s="7">
         <v>0</v>
@@ -4391,13 +4318,13 @@
         <v>0</v>
       </c>
       <c r="T26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="U26" s="7">
-        <v>3.5920955543549642E-5</v>
+        <v>3.9106637850671601E-5</v>
       </c>
       <c r="V26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="W26" s="7">
         <v>0</v>
@@ -4409,10 +4336,10 @@
         <v>0</v>
       </c>
       <c r="Z26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AA26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AB26" s="7">
         <v>0</v>
@@ -4421,19 +4348,19 @@
         <v>0</v>
       </c>
       <c r="AD26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AE26" s="7">
-        <v>1.0842613803274841E-3</v>
+        <v>1.5551171694600738E-3</v>
       </c>
       <c r="AF26" s="7">
         <v>0</v>
       </c>
       <c r="AG26" s="7">
-        <v>4.8471858771071514E-4</v>
+        <v>8.3684388025867737E-5</v>
       </c>
       <c r="AH26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AI26" s="7">
         <v>0</v>
@@ -4445,19 +4372,19 @@
         <v>0</v>
       </c>
       <c r="AL26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AM26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AN26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AO26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
       <c r="AP26" s="7">
-        <v>2.1461188548714132E-4</v>
+        <v>2.4196877068041289E-4</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
@@ -4468,128 +4395,128 @@
         <v>45</v>
       </c>
       <c r="C27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="D27" s="7">
-        <v>0.13996314816959263</v>
+        <v>0.13788383732139395</v>
       </c>
       <c r="E27" s="7">
         <v>0</v>
       </c>
       <c r="F27" s="7">
-        <v>0.21126434084151061</v>
+        <v>0.22822848836266321</v>
       </c>
       <c r="G27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="H27" s="7">
         <v>0</v>
       </c>
       <c r="I27" s="7">
-        <v>0.16876943877588471</v>
+        <v>0.1536226037508325</v>
       </c>
       <c r="J27" s="7">
-        <v>5.5830326129101451E-2</v>
+        <v>4.6713929113805695E-2</v>
       </c>
       <c r="K27" s="7">
-        <v>0.47899499209203611</v>
+        <v>0.48364945019041872</v>
       </c>
       <c r="L27" s="7">
-        <v>0.43397340973612503</v>
+        <v>0.44121062190384552</v>
       </c>
       <c r="M27" s="7">
-        <v>7.8083937384923179E-3</v>
+        <v>7.5444636065931693E-3</v>
       </c>
       <c r="N27" s="7">
         <v>0</v>
       </c>
       <c r="O27" s="7">
-        <v>0.32139240559729665</v>
+        <v>0.31534345983794904</v>
       </c>
       <c r="P27" s="7">
-        <v>4.5101854101669552E-2</v>
+        <v>4.8752125409823058E-2</v>
       </c>
       <c r="Q27" s="7">
-        <v>4.2278217409080672E-2</v>
+        <v>3.7887173910940909E-2</v>
       </c>
       <c r="R27" s="7">
-        <v>9.3762073192707171E-2</v>
+        <v>9.4092345998718907E-2</v>
       </c>
       <c r="S27" s="7">
         <v>0</v>
       </c>
       <c r="T27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="U27" s="7">
-        <v>2.7199790376984983E-2</v>
+        <v>2.54001586984542E-2</v>
       </c>
       <c r="V27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="W27" s="7">
-        <v>0.39854699941986393</v>
+        <v>0.3843396440490357</v>
       </c>
       <c r="X27" s="7">
         <v>0</v>
       </c>
       <c r="Y27" s="7">
-        <v>0.42601964136094178</v>
+        <v>0.40799899377522947</v>
       </c>
       <c r="Z27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AA27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AB27" s="7">
         <v>0</v>
       </c>
       <c r="AC27" s="7">
-        <v>4.2796101149814261E-2</v>
+        <v>4.3746128159579761E-2</v>
       </c>
       <c r="AD27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AE27" s="7">
-        <v>0.22337011857594755</v>
+        <v>0.2080868278829229</v>
       </c>
       <c r="AF27" s="7">
         <v>0</v>
       </c>
       <c r="AG27" s="7">
-        <v>0.11285731795882967</v>
+        <v>0.10279663407983926</v>
       </c>
       <c r="AH27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AI27" s="7">
-        <v>0.31553770605079418</v>
+        <v>0.33776937355978315</v>
       </c>
       <c r="AJ27" s="7">
-        <v>9.7658805477497446E-2</v>
+        <v>8.7905439975186864E-2</v>
       </c>
       <c r="AK27" s="7">
-        <v>0.13897364134771883</v>
+        <v>0.14737891754784518</v>
       </c>
       <c r="AL27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AM27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AN27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AO27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
       <c r="AP27" s="7">
-        <v>8.4609977348954285E-2</v>
+        <v>8.0527793488221769E-2</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -4724,124 +4651,124 @@
         <v>72</v>
       </c>
       <c r="C29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="D29" s="7">
-        <v>0.28401788551413309</v>
+        <v>0.36182307550129161</v>
       </c>
       <c r="E29" s="7">
-        <v>0.31880782202109564</v>
+        <v>0.27768482663326743</v>
       </c>
       <c r="F29" s="7">
-        <v>0.65512514717587444</v>
+        <v>0.65985145855886795</v>
       </c>
       <c r="G29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="H29" s="7">
-        <v>9.0869557953738925E-2</v>
+        <v>5.4073842033736844E-2</v>
       </c>
       <c r="I29" s="7">
-        <v>0.36455778929633181</v>
+        <v>0.38587432040866593</v>
       </c>
       <c r="J29" s="7">
-        <v>0.11834025390149214</v>
+        <v>0.12912472987897983</v>
       </c>
       <c r="K29" s="7">
-        <v>0.12673401605816165</v>
+        <v>0.12087940683921074</v>
       </c>
       <c r="L29" s="7">
-        <v>9.3311000811066025E-2</v>
+        <v>9.4053976946436343E-2</v>
       </c>
       <c r="M29" s="7">
-        <v>0.33843494950988973</v>
+        <v>0.26388810236486993</v>
       </c>
       <c r="N29" s="7">
-        <v>7.8E-2</v>
+        <v>0.24084493288819736</v>
       </c>
       <c r="O29" s="7">
-        <v>0.52575274151786189</v>
+        <v>0.5544557901310988</v>
       </c>
       <c r="P29" s="7">
-        <v>0.49031489588351507</v>
+        <v>0.49185028297539385</v>
       </c>
       <c r="Q29" s="7">
-        <v>0.52737666668355909</v>
+        <v>0.51091597390161658</v>
       </c>
       <c r="R29" s="7">
-        <v>0.385649562521518</v>
+        <v>0.37849984949772192</v>
       </c>
       <c r="S29" s="7">
-        <v>0.19072399314917252</v>
+        <v>0.20145948131760016</v>
       </c>
       <c r="T29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="U29" s="7">
-        <v>0.15074037648527858</v>
+        <v>9.4167376101956829E-2</v>
       </c>
       <c r="V29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="W29" s="7">
-        <v>0.17161502751574065</v>
+        <v>0.1658744976469517</v>
       </c>
       <c r="X29" s="7">
-        <v>8.2472387786670626E-2</v>
+        <v>0.12429206689317975</v>
       </c>
       <c r="Y29" s="7">
-        <v>0.14386725642849318</v>
+        <v>0.13829955771235172</v>
       </c>
       <c r="Z29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AA29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AB29" s="7">
-        <v>0.76917219045681118</v>
+        <v>0.84386414974362012</v>
       </c>
       <c r="AC29" s="7">
-        <v>8.1772840682540093E-2</v>
+        <v>0.14034031262280025</v>
       </c>
       <c r="AD29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AE29" s="7">
-        <v>6.4290860158543711E-2</v>
+        <v>2.6559404949702013E-2</v>
       </c>
       <c r="AF29" s="7">
-        <v>4.0585060164630704E-2</v>
+        <v>7.4760383626270258E-2</v>
       </c>
       <c r="AG29" s="7">
-        <v>3.9235409946888657E-2</v>
+        <v>5.2193104128761519E-2</v>
       </c>
       <c r="AH29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AI29" s="7">
-        <v>0.5582030546767861</v>
+        <v>0.54413512201634862</v>
       </c>
       <c r="AJ29" s="7">
-        <v>0.34707721743558301</v>
+        <v>0.41920623150727265</v>
       </c>
       <c r="AK29" s="7">
-        <v>0.24907126683855033</v>
+        <v>0.17363613205831183</v>
       </c>
       <c r="AL29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AM29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AN29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AO29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
       <c r="AP29" s="7">
-        <v>0.23031949530862714</v>
+        <v>0.23022554679979607</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
@@ -4852,19 +4779,19 @@
         <v>51</v>
       </c>
       <c r="C30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="D30" s="7">
         <v>0</v>
       </c>
       <c r="E30" s="7">
-        <v>0</v>
+        <v>1.3582012329218086E-4</v>
       </c>
       <c r="F30" s="7">
         <v>0</v>
       </c>
       <c r="G30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="H30" s="7">
         <v>0</v>
@@ -4873,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="7">
-        <v>0</v>
+        <v>1.5129512408637324E-5</v>
       </c>
       <c r="K30" s="7">
         <v>0</v>
@@ -4888,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="7">
-        <v>0</v>
+        <v>1.4802980645797312E-3</v>
       </c>
       <c r="P30" s="7">
         <v>0</v>
@@ -4903,13 +4830,13 @@
         <v>0</v>
       </c>
       <c r="T30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="U30" s="7">
         <v>0</v>
       </c>
       <c r="V30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="W30" s="7">
         <v>0</v>
@@ -4921,10 +4848,10 @@
         <v>0</v>
       </c>
       <c r="Z30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AA30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AB30" s="7">
         <v>0</v>
@@ -4933,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="AD30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AE30" s="7">
         <v>0</v>
@@ -4945,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="AH30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AI30" s="7">
-        <v>0</v>
+        <v>8.6228312336042738E-4</v>
       </c>
       <c r="AJ30" s="7">
         <v>0</v>
@@ -4957,19 +4884,19 @@
         <v>0</v>
       </c>
       <c r="AL30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AM30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AN30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AO30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
       <c r="AP30" s="7">
-        <v>0</v>
+        <v>1.6716977293630003E-4</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
@@ -4980,88 +4907,88 @@
         <v>53</v>
       </c>
       <c r="C31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="D31" s="7">
-        <v>0</v>
+        <v>2.5415661957452418E-4</v>
       </c>
       <c r="E31" s="7">
-        <v>0</v>
+        <v>4.1697980465715134E-4</v>
       </c>
       <c r="F31" s="7">
         <v>0</v>
       </c>
       <c r="G31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="H31" s="7">
         <v>0</v>
       </c>
       <c r="I31" s="7">
-        <v>0</v>
+        <v>9.6005856159418128E-5</v>
       </c>
       <c r="J31" s="7">
-        <v>0</v>
+        <v>1.177244675884009E-2</v>
       </c>
       <c r="K31" s="7">
-        <v>0</v>
+        <v>3.9625749117466365E-2</v>
       </c>
       <c r="L31" s="7">
-        <v>0</v>
+        <v>2.3193646118229733E-3</v>
       </c>
       <c r="M31" s="7">
         <v>0</v>
       </c>
       <c r="N31" s="7">
-        <v>0</v>
+        <v>2.1123459955294844E-4</v>
       </c>
       <c r="O31" s="7">
-        <v>0</v>
+        <v>1.5213374399411422E-5</v>
       </c>
       <c r="P31" s="7">
-        <v>0</v>
+        <v>6.5333981903863058E-3</v>
       </c>
       <c r="Q31" s="7">
         <v>0</v>
       </c>
       <c r="R31" s="7">
-        <v>0</v>
+        <v>5.8284846405357125E-4</v>
       </c>
       <c r="S31" s="7">
-        <v>0</v>
+        <v>2.4570488219233716E-4</v>
       </c>
       <c r="T31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="U31" s="7">
-        <v>0</v>
+        <v>2.4740817768722375E-3</v>
       </c>
       <c r="V31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="W31" s="7">
-        <v>0</v>
+        <v>5.9551012940256207E-4</v>
       </c>
       <c r="X31" s="7">
-        <v>0</v>
+        <v>3.4712585272026171E-3</v>
       </c>
       <c r="Y31" s="7">
         <v>0</v>
       </c>
       <c r="Z31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AA31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AB31" s="7">
         <v>0</v>
       </c>
       <c r="AC31" s="7">
-        <v>0</v>
+        <v>8.4087702162795788E-3</v>
       </c>
       <c r="AD31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AE31" s="7">
         <v>0</v>
@@ -5073,10 +5000,10 @@
         <v>0</v>
       </c>
       <c r="AH31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AI31" s="7">
-        <v>0</v>
+        <v>1.3135199186727487E-4</v>
       </c>
       <c r="AJ31" s="7">
         <v>0</v>
@@ -5085,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="AL31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AM31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AN31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AO31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
       <c r="AP31" s="7">
-        <v>0</v>
+        <v>5.1050938734229995E-3</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.25">
@@ -5236,124 +5163,124 @@
         <v>77</v>
       </c>
       <c r="C33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="D33" s="7">
-        <v>0.13715842959043084</v>
+        <v>0.14475595983447442</v>
       </c>
       <c r="E33" s="7">
-        <v>3.6657279513507945E-2</v>
+        <v>5.66719703960065E-2</v>
       </c>
       <c r="F33" s="7">
-        <v>4.6457402070773847E-2</v>
+        <v>4.9785848666441278E-2</v>
       </c>
       <c r="G33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="H33" s="7">
-        <v>0.84384304180356551</v>
+        <v>0.88637530225053573</v>
       </c>
       <c r="I33" s="7">
-        <v>2.9269117003199948E-2</v>
+        <v>3.9182766016364293E-2</v>
       </c>
       <c r="J33" s="7">
-        <v>0.10124785471370093</v>
+        <v>0.11534095873571577</v>
       </c>
       <c r="K33" s="7">
-        <v>4.099151591566641E-2</v>
+        <v>6.4462760938859318E-2</v>
       </c>
       <c r="L33" s="7">
         <v>0</v>
       </c>
       <c r="M33" s="7">
-        <v>0.55040318457778947</v>
+        <v>0.59410752802422828</v>
       </c>
       <c r="N33" s="7">
-        <v>0</v>
+        <v>0.20354212820748727</v>
       </c>
       <c r="O33" s="7">
-        <v>7.9950166337527558E-3</v>
+        <v>8.4904472742949044E-3</v>
       </c>
       <c r="P33" s="7">
-        <v>6.1574207750902825E-2</v>
+        <v>9.3633370507156088E-2</v>
       </c>
       <c r="Q33" s="7">
-        <v>7.6343202777516564E-2</v>
+        <v>7.1412615938876114E-2</v>
       </c>
       <c r="R33" s="7">
-        <v>3.1820551245302212E-2</v>
+        <v>3.5067503099387463E-2</v>
       </c>
       <c r="S33" s="7">
-        <v>3.7443155237436507E-2</v>
+        <v>4.1590101105001859E-2</v>
       </c>
       <c r="T33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="U33" s="7">
-        <v>8.5473965248816619E-2</v>
+        <v>0.13384147581469297</v>
       </c>
       <c r="V33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="W33" s="7">
         <v>0</v>
       </c>
       <c r="X33" s="7">
-        <v>0.10994786019054971</v>
+        <v>0.11786083137739874</v>
       </c>
       <c r="Y33" s="7">
         <v>0</v>
       </c>
       <c r="Z33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AA33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AB33" s="7">
-        <v>0.23082780954318913</v>
+        <v>0.15613585025638019</v>
       </c>
       <c r="AC33" s="7">
-        <v>3.3823297228610216E-2</v>
+        <v>6.2354052632882885E-2</v>
       </c>
       <c r="AD33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AE33" s="7">
-        <v>5.170246986412546E-2</v>
+        <v>6.8711379653984231E-2</v>
       </c>
       <c r="AF33" s="7">
-        <v>0.21707855186725816</v>
+        <v>0.2427652163246766</v>
       </c>
       <c r="AG33" s="7">
         <v>0</v>
       </c>
       <c r="AH33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AI33" s="7">
-        <v>2.0576804519565273E-2</v>
+        <v>1.8291281283682084E-2</v>
       </c>
       <c r="AJ33" s="7">
-        <v>8.5599229480046446E-2</v>
+        <v>5.2992831040146973E-2</v>
       </c>
       <c r="AK33" s="7">
-        <v>3.4486427879306822E-2</v>
+        <v>3.5629899572582259E-2</v>
       </c>
       <c r="AL33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AM33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AN33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AO33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
       <c r="AP33" s="7">
-        <v>9.354662980001037E-2</v>
+        <v>0.11739127451571586</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
@@ -5492,19 +5419,19 @@
         <v>31</v>
       </c>
       <c r="C35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="D35" s="7">
-        <v>1.5210400919677826E-4</v>
+        <v>1.300962403965224E-5</v>
       </c>
       <c r="E35" s="7">
         <v>0</v>
       </c>
       <c r="F35" s="7">
-        <v>6.7600262404796151E-3</v>
+        <v>6.8946765704723403E-4</v>
       </c>
       <c r="G35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="H35" s="7">
         <v>0</v>
@@ -5525,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="7">
-        <v>3.3110364880840088E-3</v>
+        <v>0</v>
       </c>
       <c r="O35" s="7">
         <v>0</v>
@@ -5543,28 +5470,28 @@
         <v>0</v>
       </c>
       <c r="T35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="U35" s="7">
         <v>0</v>
       </c>
       <c r="V35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="W35" s="7">
-        <v>5.9355879717974897E-3</v>
+        <v>3.9194684881784635E-3</v>
       </c>
       <c r="X35" s="7">
         <v>0</v>
       </c>
       <c r="Y35" s="7">
-        <v>9.5475787756645546E-6</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AA35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AB35" s="7">
         <v>0</v>
@@ -5573,19 +5500,19 @@
         <v>0</v>
       </c>
       <c r="AD35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AE35" s="7">
-        <v>5.2759784662458536E-2</v>
+        <v>5.2527975081316028E-2</v>
       </c>
       <c r="AF35" s="7">
         <v>0</v>
       </c>
       <c r="AG35" s="7">
-        <v>5.694673227563311E-3</v>
+        <v>7.0135633367118446E-3</v>
       </c>
       <c r="AH35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AI35" s="7">
         <v>0</v>
@@ -5594,22 +5521,22 @@
         <v>0</v>
       </c>
       <c r="AK35" s="7">
-        <v>2.1888187384511395E-2</v>
+        <v>2.9477872539607746E-3</v>
       </c>
       <c r="AL35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AM35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AN35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AO35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
       <c r="AP35" s="7">
-        <v>4.8164402873198744E-3</v>
+        <v>3.2134205331506159E-3</v>
       </c>
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
@@ -5620,25 +5547,25 @@
         <v>33</v>
       </c>
       <c r="C36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="D36" s="7">
-        <v>1.9274957429102739E-3</v>
+        <v>7.8887320765562126E-4</v>
       </c>
       <c r="E36" s="7">
-        <v>3.2131361259559482E-2</v>
+        <v>3.9009527159343575E-2</v>
       </c>
       <c r="F36" s="7">
-        <v>7.3721150267408941E-2</v>
+        <v>4.6270158368191865E-2</v>
       </c>
       <c r="G36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="H36" s="7">
-        <v>0.50925428249925864</v>
+        <v>0.61153005075392364</v>
       </c>
       <c r="I36" s="7">
-        <v>1.4412451208639822E-2</v>
+        <v>1.3117712093086469E-2</v>
       </c>
       <c r="J36" s="7">
         <v>0</v>
@@ -5647,97 +5574,97 @@
         <v>0</v>
       </c>
       <c r="L36" s="7">
-        <v>7.1302628591431619E-2</v>
+        <v>6.7465561939624344E-2</v>
       </c>
       <c r="M36" s="7">
-        <v>0.16525979128772589</v>
+        <v>0.17068868181107183</v>
       </c>
       <c r="N36" s="7">
-        <v>0.11844654070077444</v>
+        <v>0.11729455429978344</v>
       </c>
       <c r="O36" s="7">
-        <v>5.5581870575920608E-2</v>
+        <v>3.8106223287743851E-2</v>
       </c>
       <c r="P36" s="7">
-        <v>0.15926242100410806</v>
+        <v>0.11344689292617038</v>
       </c>
       <c r="Q36" s="7">
-        <v>0.21778049229761315</v>
+        <v>0.184818200131839</v>
       </c>
       <c r="R36" s="7">
-        <v>0.19802544589436782</v>
+        <v>0.20794290394466683</v>
       </c>
       <c r="S36" s="7">
-        <v>1.286006948413358E-2</v>
+        <v>1.5801783044136809E-2</v>
       </c>
       <c r="T36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="U36" s="7">
-        <v>0.12381704827611574</v>
+        <v>0.15588773573772449</v>
       </c>
       <c r="V36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="W36" s="7">
-        <v>0.31875990403424886</v>
+        <v>0.54269756293740401</v>
       </c>
       <c r="X36" s="7">
-        <v>1.8602488135434098E-2</v>
+        <v>1.1015585095345113E-2</v>
       </c>
       <c r="Y36" s="7">
-        <v>0.2506052260540354</v>
+        <v>0.38620525339988315</v>
       </c>
       <c r="Z36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AA36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AB36" s="7">
-        <v>0.77370046041156382</v>
+        <v>0.66605437649535726</v>
       </c>
       <c r="AC36" s="7">
         <v>0</v>
       </c>
       <c r="AD36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AE36" s="7">
-        <v>0.42333549902515721</v>
+        <v>0.55642703514094149</v>
       </c>
       <c r="AF36" s="7">
-        <v>0.17262928491174362</v>
+        <v>0.14089298222901842</v>
       </c>
       <c r="AG36" s="7">
-        <v>0.45405925282392984</v>
+        <v>0.48145003780205975</v>
       </c>
       <c r="AH36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AI36" s="7">
         <v>0</v>
       </c>
       <c r="AJ36" s="7">
-        <v>0.23758933742786198</v>
+        <v>0.20428802739853366</v>
       </c>
       <c r="AK36" s="7">
-        <v>1.5649516940558408E-2</v>
+        <v>1.2420791164373677E-2</v>
       </c>
       <c r="AL36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AM36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AN36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AO36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
       <c r="AP36" s="7">
-        <v>0.12976890625339038</v>
+        <v>0.12461660694677959</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
@@ -5748,124 +5675,124 @@
         <v>39</v>
       </c>
       <c r="C37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="D37" s="7">
-        <v>4.0560845688941603E-2</v>
+        <v>2.2057008279264052E-2</v>
       </c>
       <c r="E37" s="7">
-        <v>0.21586572179766073</v>
+        <v>0.24984613154826521</v>
       </c>
       <c r="F37" s="7">
-        <v>2.0431394894335202E-2</v>
+        <v>1.6991971068483675E-2</v>
       </c>
       <c r="G37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="H37" s="7">
         <v>0</v>
       </c>
       <c r="I37" s="7">
-        <v>0.27380538891425765</v>
+        <v>0.23886496490398093</v>
       </c>
       <c r="J37" s="7">
-        <v>3.6218321442252441E-2</v>
+        <v>2.7948393129793768E-2</v>
       </c>
       <c r="K37" s="7">
-        <v>1.6329433576856556E-2</v>
+        <v>1.8851773795113894E-2</v>
       </c>
       <c r="L37" s="7">
-        <v>6.5143347345640396E-2</v>
+        <v>4.937786975946265E-2</v>
       </c>
       <c r="M37" s="7">
-        <v>6.5493045001895822E-3</v>
+        <v>1.0387533723445282E-2</v>
       </c>
       <c r="N37" s="7">
-        <v>0.27352654873922244</v>
+        <v>0.24354276344939257</v>
       </c>
       <c r="O37" s="7">
-        <v>4.3240553639112781E-3</v>
+        <v>1.5153646702619399E-3</v>
       </c>
       <c r="P37" s="7">
-        <v>0.27047151663813357</v>
+        <v>0.24844968508610085</v>
       </c>
       <c r="Q37" s="7">
-        <v>0.21216705755357546</v>
+        <v>0.2252463154322791</v>
       </c>
       <c r="R37" s="7">
-        <v>0.58549739376993237</v>
+        <v>0.52853329954679851</v>
       </c>
       <c r="S37" s="7">
-        <v>0.15718234751005616</v>
+        <v>0.15459649444562737</v>
       </c>
       <c r="T37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="U37" s="7">
-        <v>0.55719038643756746</v>
+        <v>0.50592835259557767</v>
       </c>
       <c r="V37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="W37" s="7">
-        <v>0.14572237994687884</v>
+        <v>0.12447950014889834</v>
       </c>
       <c r="X37" s="7">
-        <v>0.58395787840879154</v>
+        <v>0.52253157272307416</v>
       </c>
       <c r="Y37" s="7">
-        <v>9.8173510604520023E-2</v>
+        <v>7.8799416127480884E-2</v>
       </c>
       <c r="Z37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AA37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AB37" s="7">
         <v>0</v>
       </c>
       <c r="AC37" s="7">
-        <v>0.57704370891184698</v>
+        <v>0.60291701730555114</v>
       </c>
       <c r="AD37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AE37" s="7">
-        <v>0.22022731900998338</v>
+        <v>0.22910041370060549</v>
       </c>
       <c r="AF37" s="7">
-        <v>0.11514852373134017</v>
+        <v>9.582427946131232E-2</v>
       </c>
       <c r="AG37" s="7">
-        <v>0.41984426116820556</v>
+        <v>0.38844352203495414</v>
       </c>
       <c r="AH37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AI37" s="7">
-        <v>2.677844152083316E-3</v>
+        <v>2.3287306317375787E-3</v>
       </c>
       <c r="AJ37" s="7">
-        <v>8.3185024074684172E-2</v>
+        <v>7.2283609821396103E-2</v>
       </c>
       <c r="AK37" s="7">
-        <v>0.44899403236469804</v>
+        <v>0.42581845857407213</v>
       </c>
       <c r="AL37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AM37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AN37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AO37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
       <c r="AP37" s="7">
-        <v>0.22838282599891488</v>
+        <v>0.20045485902714544</v>
       </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.25">
@@ -5876,25 +5803,25 @@
         <v>41</v>
       </c>
       <c r="C38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="D38" s="7">
-        <v>2.8508434700509361E-2</v>
+        <v>1.8316638778314829E-2</v>
       </c>
       <c r="E38" s="7">
         <v>0</v>
       </c>
       <c r="F38" s="7">
-        <v>8.5557578234109671E-2</v>
+        <v>6.720420366693422E-2</v>
       </c>
       <c r="G38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="H38" s="7">
         <v>0</v>
       </c>
       <c r="I38" s="7">
-        <v>1.7483089729421013E-2</v>
+        <v>1.1778985948878747E-2</v>
       </c>
       <c r="J38" s="7">
         <v>0</v>
@@ -5903,13 +5830,13 @@
         <v>0</v>
       </c>
       <c r="L38" s="7">
-        <v>0.23976765757182675</v>
+        <v>0.24257236090859413</v>
       </c>
       <c r="M38" s="7">
-        <v>8.3278072220387925E-2</v>
+        <v>2.5102778257582434E-2</v>
       </c>
       <c r="N38" s="7">
-        <v>1.3800103212750017E-2</v>
+        <v>1.4272733972659827E-2</v>
       </c>
       <c r="O38" s="7">
         <v>0</v>
@@ -5918,37 +5845,37 @@
         <v>0</v>
       </c>
       <c r="Q38" s="7">
-        <v>8.6745935341156183E-2</v>
+        <v>6.7706377878848936E-2</v>
       </c>
       <c r="R38" s="7">
-        <v>1.063067998010188E-3</v>
+        <v>1.2858849339219228E-3</v>
       </c>
       <c r="S38" s="7">
         <v>0</v>
       </c>
       <c r="T38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="U38" s="7">
-        <v>2.8427008386287717E-2</v>
+        <v>3.292770666162307E-2</v>
       </c>
       <c r="V38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="W38" s="7">
-        <v>0.10824763796224975</v>
+        <v>0.10384545814073688</v>
       </c>
       <c r="X38" s="7">
         <v>0</v>
       </c>
       <c r="Y38" s="7">
-        <v>0.37923373632579266</v>
+        <v>0.32106666119554716</v>
       </c>
       <c r="Z38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AA38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AB38" s="7">
         <v>0</v>
@@ -5957,43 +5884,43 @@
         <v>0</v>
       </c>
       <c r="AD38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AE38" s="7">
-        <v>8.7032339378295714E-2</v>
+        <v>8.7166229493703867E-2</v>
       </c>
       <c r="AF38" s="7">
-        <v>0.21847450080160974</v>
+        <v>0.21185518320959157</v>
       </c>
       <c r="AG38" s="7">
-        <v>0.11046157217815319</v>
+        <v>0.11159537746012087</v>
       </c>
       <c r="AH38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AI38" s="7">
         <v>0</v>
       </c>
       <c r="AJ38" s="7">
-        <v>8.4898115933734711E-2</v>
+        <v>7.3575449192760656E-2</v>
       </c>
       <c r="AK38" s="7">
-        <v>1.5154714144175591E-2</v>
+        <v>9.7769395760764002E-3</v>
       </c>
       <c r="AL38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AM38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AN38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AO38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
       <c r="AP38" s="7">
-        <v>3.5767702784609764E-2</v>
+        <v>3.2583767789043663E-2</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
@@ -6004,124 +5931,124 @@
         <v>72</v>
       </c>
       <c r="C39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="D39" s="7">
-        <v>0.92885111985844149</v>
+        <v>0.95882447011072591</v>
       </c>
       <c r="E39" s="7">
-        <v>0.7520029169427801</v>
+        <v>0.71114434129239101</v>
       </c>
       <c r="F39" s="7">
-        <v>0.81352985036366632</v>
+        <v>0.86884419923934297</v>
       </c>
       <c r="G39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="H39" s="7">
-        <v>0.49074571750074136</v>
+        <v>0.38846994924607653</v>
       </c>
       <c r="I39" s="7">
-        <v>0.69429907014768155</v>
+        <v>0.73623833705405395</v>
       </c>
       <c r="J39" s="7">
-        <v>0.96378167855774755</v>
+        <v>0.9720516068702062</v>
       </c>
       <c r="K39" s="7">
-        <v>0.98367056642314332</v>
+        <v>0.98114822620488595</v>
       </c>
       <c r="L39" s="7">
-        <v>0.62378636649110131</v>
+        <v>0.64058420739231881</v>
       </c>
       <c r="M39" s="7">
-        <v>0.74491283199169678</v>
+        <v>0.79382100620790008</v>
       </c>
       <c r="N39" s="7">
-        <v>0.59091577085916913</v>
+        <v>0.62488994827816413</v>
       </c>
       <c r="O39" s="7">
-        <v>0.94009407406016809</v>
+        <v>0.96037841204199437</v>
       </c>
       <c r="P39" s="7">
-        <v>0.57026606235775845</v>
+        <v>0.63810342198772851</v>
       </c>
       <c r="Q39" s="7">
-        <v>0.48330651480765541</v>
+        <v>0.52222910655703303</v>
       </c>
       <c r="R39" s="7">
-        <v>0.21541409233768968</v>
+        <v>0.2622379115746129</v>
       </c>
       <c r="S39" s="7">
-        <v>0.82995758300581024</v>
+        <v>0.82960172251023578</v>
       </c>
       <c r="T39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="U39" s="7">
-        <v>0.29056555690002905</v>
+        <v>0.30525620500507489</v>
       </c>
       <c r="V39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="W39" s="7">
-        <v>0.42133449008482488</v>
+        <v>0.22505801028478253</v>
       </c>
       <c r="X39" s="7">
-        <v>0.39743963345577427</v>
+        <v>0.46645284218158062</v>
       </c>
       <c r="Y39" s="7">
-        <v>0.27197797943687635</v>
+        <v>0.21392866927708859</v>
       </c>
       <c r="Z39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AA39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AB39" s="7">
-        <v>0.22629953958843604</v>
+        <v>0.33394562350464263</v>
       </c>
       <c r="AC39" s="7">
-        <v>0.42295629108815314</v>
+        <v>0.39708298269444881</v>
       </c>
       <c r="AD39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AE39" s="7">
-        <v>0.2166450579241051</v>
+        <v>7.4778346583433006E-2</v>
       </c>
       <c r="AF39" s="7">
-        <v>0.4937476905553066</v>
+        <v>0.55142755510007757</v>
       </c>
       <c r="AG39" s="7">
-        <v>9.9402406021479334E-3</v>
+        <v>1.1497499366153558E-2</v>
       </c>
       <c r="AH39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AI39" s="7">
-        <v>0.99732215584791672</v>
+        <v>0.99767126936826178</v>
       </c>
       <c r="AJ39" s="7">
-        <v>0.59432752256371935</v>
+        <v>0.64985291358730968</v>
       </c>
       <c r="AK39" s="7">
-        <v>0.49831354916605636</v>
+        <v>0.54903602343151692</v>
       </c>
       <c r="AL39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AM39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AN39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AO39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
       <c r="AP39" s="7">
-        <v>0.60126412467576518</v>
+        <v>0.63913134570388075</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
@@ -6638,7 +6565,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>